--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>usdtry</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dis_varliklar</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dis_yukumlulukler</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>kamu_mevduati</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>banka_mevduati</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_alim</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>swap_satim</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>net_swap</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>net_rezerv_swap_dahil</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>net_rezerv_swap_haric</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dis_varliklar_tl</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dis_yukumlulukler_tl</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>kamu_mevduati_tl</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>banka_mevduati_tl</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44823</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44824</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44825</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44826</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44830</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44831</v>
       </c>
       <c r="B8" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44832</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44833</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44837</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44838</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44839</v>
       </c>
       <c r="B14" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44840</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44844</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44845</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44847</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44851</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44852</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44875</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44879</v>
       </c>
       <c r="B42" t="n">
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44880</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44881</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44882</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44886</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44889</v>
       </c>
       <c r="B50" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44893</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44900</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44901</v>
       </c>
       <c r="B58" t="n">
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44902</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44903</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44907</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44908</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44909</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44910</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44914</v>
       </c>
       <c r="B67" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="B68" t="n">
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44916</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44917</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44921</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44922</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44923</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44924</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B76" t="n">
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44928</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44929</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44930</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44931</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44935</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44936</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44937</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44938</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44943</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44944</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44945</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44949</v>
       </c>
       <c r="B92" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44950</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44952</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="B105" t="n">
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="B110" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44977</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="B113" t="n">
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44987</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44991</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44992</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44998</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44999</v>
       </c>
       <c r="B128" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45000</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45001</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45005</v>
       </c>
       <c r="B132" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45006</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45007</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="B135" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45013</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="B139" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45015</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45019</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45020</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45021</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45027</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45028</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45029</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45033</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45034</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45035</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="B161" t="n">
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="B166" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45057</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45061</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45062</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45063</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45064</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45068</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45071</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45075</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45076</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45082</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45083</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45084</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45085</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B188" t="n">
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45090</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45091</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45092</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45097</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45098</v>
       </c>
       <c r="B196" t="n">
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45104</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45111</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45112</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45113</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B206" t="n">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45118</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45119</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45120</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45125</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45126</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="B218" t="n">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B220" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="B223" t="n">
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45148</v>
       </c>
       <c r="B229" t="n">
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45152</v>
       </c>
       <c r="B231" t="n">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45153</v>
       </c>
       <c r="B232" t="n">
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45154</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45155</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45159</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45160</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45161</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45167</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B243" t="n">
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45173</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45174</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45175</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45176</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45182</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45183</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45187</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45188</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45190</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45194</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45195</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45196</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45197</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45201</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45202</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45203</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45204</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45208</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45209</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45210</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45211</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B274" t="n">
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45215</v>
       </c>
       <c r="B275" t="n">
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>45216</v>
       </c>
       <c r="B276" t="n">
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>45218</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B279" t="n">
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="B282" t="n">
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>45236</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>45239</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>45244</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>45245</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>45246</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>45250</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>45252</v>
       </c>
       <c r="B302" t="n">
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>45253</v>
       </c>
       <c r="B303" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>45257</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>45258</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="B307" t="n">
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>45264</v>
       </c>
       <c r="B310" t="n">
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>45265</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>45266</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>45267</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B314" t="n">
@@ -15209,7 +15221,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>45271</v>
       </c>
       <c r="B315" t="n">
@@ -15256,7 +15268,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>45272</v>
       </c>
       <c r="B316" t="n">
@@ -15303,7 +15315,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>45273</v>
       </c>
       <c r="B317" t="n">
@@ -15350,7 +15362,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>45274</v>
       </c>
       <c r="B318" t="n">
@@ -15397,7 +15409,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B319" t="n">
@@ -15444,7 +15456,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="B320" t="n">
@@ -15491,7 +15503,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="B321" t="n">
@@ -15538,7 +15550,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="B322" t="n">
@@ -15585,7 +15597,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>45281</v>
       </c>
       <c r="B323" t="n">
@@ -15632,7 +15644,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B324" t="n">
@@ -15679,7 +15691,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>45285</v>
       </c>
       <c r="B325" t="n">
@@ -15726,7 +15738,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>45286</v>
       </c>
       <c r="B326" t="n">
@@ -15773,7 +15785,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>45287</v>
       </c>
       <c r="B327" t="n">
@@ -15820,7 +15832,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>45288</v>
       </c>
       <c r="B328" t="n">
@@ -15867,7 +15879,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B329" t="n">
@@ -15914,7 +15926,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>45293</v>
       </c>
       <c r="B330" t="n">
@@ -15961,7 +15973,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>45294</v>
       </c>
       <c r="B331" t="n">
@@ -16008,7 +16020,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>45295</v>
       </c>
       <c r="B332" t="n">
@@ -16055,7 +16067,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B333" t="n">
@@ -16102,7 +16114,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>45299</v>
       </c>
       <c r="B334" t="n">
@@ -16149,7 +16161,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>45300</v>
       </c>
       <c r="B335" t="n">
@@ -16196,7 +16208,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>45301</v>
       </c>
       <c r="B336" t="n">
@@ -16243,7 +16255,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>45302</v>
       </c>
       <c r="B337" t="n">
@@ -16290,7 +16302,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B338" t="n">
@@ -16337,7 +16349,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B339" t="n">
@@ -16384,7 +16396,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>45307</v>
       </c>
       <c r="B340" t="n">
@@ -16431,7 +16443,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="B341" t="n">
@@ -16478,7 +16490,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>45309</v>
       </c>
       <c r="B342" t="n">
@@ -16525,7 +16537,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B343" t="n">
@@ -16572,7 +16584,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="B344" t="n">
@@ -16619,7 +16631,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>45314</v>
       </c>
       <c r="B345" t="n">
@@ -16666,7 +16678,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>45315</v>
       </c>
       <c r="B346" t="n">
@@ -16713,7 +16725,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="B347" t="n">
@@ -16760,7 +16772,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B348" t="n">
@@ -16807,7 +16819,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="B349" t="n">
@@ -16854,7 +16866,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="B350" t="n">
@@ -16901,7 +16913,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B351" t="n">
@@ -16948,7 +16960,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B352" t="n">
@@ -16995,7 +17007,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B353" t="n">
@@ -17042,7 +17054,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="B354" t="n">
@@ -17089,7 +17101,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="B355" t="n">
@@ -17136,7 +17148,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="B356" t="n">
@@ -17183,7 +17195,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="B357" t="n">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B358" t="n">
@@ -17277,7 +17289,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B359" t="n">
@@ -17324,7 +17336,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="B360" t="n">
@@ -17371,7 +17383,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="B361" t="n">
@@ -17418,7 +17430,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="B362" t="n">
@@ -17465,7 +17477,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B363" t="n">
@@ -17512,7 +17524,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>45341</v>
       </c>
       <c r="B364" t="n">
@@ -17559,7 +17571,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="B365" t="n">
@@ -17606,7 +17618,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="B366" t="n">
@@ -17653,7 +17665,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="B367" t="n">
@@ -17700,7 +17712,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B368" t="n">
@@ -17747,7 +17759,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="B369" t="n">
@@ -17794,7 +17806,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="B370" t="n">
@@ -17841,7 +17853,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="B371" t="n">
@@ -17888,7 +17900,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B372" t="n">
@@ -17935,7 +17947,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B373" t="n">
@@ -17982,7 +17994,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>45355</v>
       </c>
       <c r="B374" t="n">
@@ -18029,7 +18041,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>45356</v>
       </c>
       <c r="B375" t="n">
@@ -18076,7 +18088,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>45357</v>
       </c>
       <c r="B376" t="n">
@@ -18123,7 +18135,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>45358</v>
       </c>
       <c r="B377" t="n">
@@ -18170,7 +18182,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B378" t="n">
@@ -18217,7 +18229,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>45362</v>
       </c>
       <c r="B379" t="n">
@@ -18264,7 +18276,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>45363</v>
       </c>
       <c r="B380" t="n">
@@ -18311,7 +18323,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="B381" t="n">
@@ -18358,7 +18370,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>45365</v>
       </c>
       <c r="B382" t="n">
@@ -18405,7 +18417,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B383" t="n">
@@ -18452,7 +18464,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="B384" t="n">
@@ -18499,7 +18511,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>45370</v>
       </c>
       <c r="B385" t="n">
@@ -18546,7 +18558,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="B386" t="n">
@@ -18593,7 +18605,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="B387" t="n">
@@ -18640,7 +18652,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B388" t="n">
@@ -18687,7 +18699,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="B389" t="n">
@@ -18734,7 +18746,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>45377</v>
       </c>
       <c r="B390" t="n">
@@ -18781,7 +18793,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>45378</v>
       </c>
       <c r="B391" t="n">
@@ -18828,7 +18840,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>45379</v>
       </c>
       <c r="B392" t="n">
@@ -18875,7 +18887,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B393" t="n">
@@ -18922,7 +18934,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B394" t="n">
@@ -18969,7 +18981,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>45384</v>
       </c>
       <c r="B395" t="n">
@@ -19016,7 +19028,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="B396" t="n">
@@ -19063,7 +19075,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>45386</v>
       </c>
       <c r="B397" t="n">
@@ -19110,7 +19122,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B398" t="n">
@@ -19157,7 +19169,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B399" t="n">
@@ -19204,7 +19216,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>45391</v>
       </c>
       <c r="B400" t="n">
@@ -19251,7 +19263,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B401" t="n">
@@ -19298,7 +19310,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>45398</v>
       </c>
       <c r="B402" t="n">
@@ -19345,7 +19357,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>45399</v>
       </c>
       <c r="B403" t="n">
@@ -19392,7 +19404,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>45400</v>
       </c>
       <c r="B404" t="n">
@@ -19439,7 +19451,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B405" t="n">
@@ -19486,7 +19498,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>45404</v>
       </c>
       <c r="B406" t="n">
@@ -19533,7 +19545,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="B407" t="n">
@@ -19580,7 +19592,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="B408" t="n">
@@ -19627,7 +19639,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B409" t="n">
@@ -19674,7 +19686,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="B410" t="n">
@@ -19721,7 +19733,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B411" t="n">
@@ -19768,7 +19780,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="B412" t="n">
@@ -19815,7 +19827,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B413" t="n">
@@ -19862,7 +19874,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="B414" t="n">
@@ -19909,7 +19921,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="B415" t="n">
@@ -19956,7 +19968,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="B416" t="n">
@@ -20003,7 +20015,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>45421</v>
       </c>
       <c r="B417" t="n">
@@ -20050,7 +20062,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B418" t="n">
@@ -20097,7 +20109,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>45425</v>
       </c>
       <c r="B419" t="n">
@@ -20144,7 +20156,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>45426</v>
       </c>
       <c r="B420" t="n">
@@ -20191,7 +20203,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>45427</v>
       </c>
       <c r="B421" t="n">
@@ -20238,7 +20250,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>45428</v>
       </c>
       <c r="B422" t="n">
@@ -20285,7 +20297,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B423" t="n">
@@ -20332,7 +20344,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>45432</v>
       </c>
       <c r="B424" t="n">
@@ -20379,7 +20391,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="B425" t="n">
@@ -20426,7 +20438,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>45434</v>
       </c>
       <c r="B426" t="n">
@@ -20473,7 +20485,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="B427" t="n">
@@ -20520,7 +20532,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B428" t="n">
@@ -20567,7 +20579,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>45439</v>
       </c>
       <c r="B429" t="n">
@@ -20614,7 +20626,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45440</v>
       </c>
       <c r="B430" t="n">
@@ -20661,7 +20673,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="B431" t="n">
@@ -20708,7 +20720,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="B432" t="n">
@@ -20755,7 +20767,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B433" t="n">
@@ -20802,7 +20814,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B434" t="n">
@@ -20849,7 +20861,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45447</v>
       </c>
       <c r="B435" t="n">
@@ -20896,7 +20908,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45448</v>
       </c>
       <c r="B436" t="n">
@@ -20943,7 +20955,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="B437" t="n">
@@ -20990,7 +21002,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B438" t="n">
@@ -21037,7 +21049,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="B439" t="n">
@@ -21084,7 +21096,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45454</v>
       </c>
       <c r="B440" t="n">
@@ -21131,7 +21143,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45455</v>
       </c>
       <c r="B441" t="n">
@@ -21178,7 +21190,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45456</v>
       </c>
       <c r="B442" t="n">
@@ -21225,7 +21237,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B443" t="n">
@@ -21272,7 +21284,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="B444" t="n">
@@ -21319,7 +21331,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B445" t="n">
@@ -21366,7 +21378,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B446" t="n">
@@ -21413,7 +21425,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B447" t="n">
@@ -21460,7 +21472,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="B448" t="n">
@@ -21507,7 +21519,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B449" t="n">
@@ -21554,7 +21566,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B450" t="n">
@@ -21601,7 +21613,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B451" t="n">
@@ -21648,7 +21660,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B452" t="n">
@@ -21695,7 +21707,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45476</v>
       </c>
       <c r="B453" t="n">
@@ -21742,7 +21754,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45477</v>
       </c>
       <c r="B454" t="n">
@@ -21789,7 +21801,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B455" t="n">
@@ -21836,7 +21848,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B456" t="n">
@@ -21883,7 +21895,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B457" t="n">
@@ -21930,7 +21942,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45483</v>
       </c>
       <c r="B458" t="n">
@@ -21977,7 +21989,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="B459" t="n">
@@ -22024,7 +22036,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B460" t="n">
@@ -22071,7 +22083,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45489</v>
       </c>
       <c r="B461" t="n">
@@ -22118,7 +22130,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B462" t="n">
@@ -22165,7 +22177,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45491</v>
       </c>
       <c r="B463" t="n">
@@ -22212,7 +22224,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B464" t="n">
@@ -22259,7 +22271,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="B465" t="n">
@@ -22306,7 +22318,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="B466" t="n">
@@ -22353,7 +22365,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="B467" t="n">
@@ -22400,7 +22412,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="B468" t="n">
@@ -22447,7 +22459,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B469" t="n">
@@ -22494,7 +22506,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B470" t="n">
@@ -22541,7 +22553,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="B471" t="n">
@@ -22588,7 +22600,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B472" t="n">
@@ -22635,7 +22647,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B473" t="n">
@@ -22682,7 +22694,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B474" t="n">
@@ -22729,7 +22741,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="B475" t="n">
@@ -22776,7 +22788,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="B476" t="n">
@@ -22823,7 +22835,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="B477" t="n">
@@ -22870,7 +22882,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="B478" t="n">
@@ -22917,7 +22929,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B479" t="n">
@@ -22964,7 +22976,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="B480" t="n">
@@ -23011,7 +23023,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45517</v>
       </c>
       <c r="B481" t="n">
@@ -23058,7 +23070,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45518</v>
       </c>
       <c r="B482" t="n">
@@ -23105,7 +23117,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45519</v>
       </c>
       <c r="B483" t="n">
@@ -23152,7 +23164,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B484" t="n">
@@ -23199,7 +23211,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B485" t="n">
@@ -23246,7 +23258,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45524</v>
       </c>
       <c r="B486" t="n">
@@ -23293,7 +23305,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45525</v>
       </c>
       <c r="B487" t="n">
@@ -23340,7 +23352,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="B488" t="n">
@@ -23387,7 +23399,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B489" t="n">
@@ -23434,7 +23446,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45530</v>
       </c>
       <c r="B490" t="n">
@@ -23481,7 +23493,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45531</v>
       </c>
       <c r="B491" t="n">
@@ -23528,7 +23540,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45532</v>
       </c>
       <c r="B492" t="n">
@@ -23575,7 +23587,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="B493" t="n">
@@ -23622,7 +23634,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B494" t="n">
@@ -23669,7 +23681,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45538</v>
       </c>
       <c r="B495" t="n">
@@ -23716,7 +23728,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45539</v>
       </c>
       <c r="B496" t="n">
@@ -23763,7 +23775,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="B497" t="n">
@@ -23810,7 +23822,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B498" t="n">
@@ -23857,7 +23869,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B499" t="n">
@@ -23904,7 +23916,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="B500" t="n">
@@ -23951,7 +23963,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45546</v>
       </c>
       <c r="B501" t="n">
@@ -23998,7 +24010,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45547</v>
       </c>
       <c r="B502" t="n">
@@ -24045,7 +24057,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B503" t="n">
@@ -24092,7 +24104,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B504" t="n">
@@ -24139,7 +24151,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45552</v>
       </c>
       <c r="B505" t="n">
@@ -24186,7 +24198,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="B506" t="n">
@@ -24233,7 +24245,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45554</v>
       </c>
       <c r="B507" t="n">
@@ -24280,7 +24292,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B508" t="n">
@@ -24327,7 +24339,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B509" t="n">
@@ -24374,7 +24386,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45559</v>
       </c>
       <c r="B510" t="n">
@@ -24421,7 +24433,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="B511" t="n">
@@ -24468,7 +24480,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45561</v>
       </c>
       <c r="B512" t="n">
@@ -24515,7 +24527,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B513" t="n">
@@ -24562,7 +24574,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B514" t="n">
@@ -24609,7 +24621,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B515" t="n">
@@ -24656,7 +24668,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45567</v>
       </c>
       <c r="B516" t="n">
@@ -24703,7 +24715,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45568</v>
       </c>
       <c r="B517" t="n">
@@ -24750,7 +24762,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B518" t="n">
@@ -24797,7 +24809,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B519" t="n">
@@ -24844,7 +24856,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45573</v>
       </c>
       <c r="B520" t="n">
@@ -24891,7 +24903,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="B521" t="n">
@@ -24938,7 +24950,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45575</v>
       </c>
       <c r="B522" t="n">
@@ -24985,7 +24997,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B523" t="n">
@@ -25032,7 +25044,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B524" t="n">
@@ -25079,7 +25091,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45580</v>
       </c>
       <c r="B525" t="n">
@@ -25126,7 +25138,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45581</v>
       </c>
       <c r="B526" t="n">
@@ -25173,7 +25185,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="B527" t="n">
@@ -25220,7 +25232,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B528" t="n">
@@ -25267,7 +25279,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B529" t="n">
@@ -25314,7 +25326,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="B530" t="n">
@@ -25361,7 +25373,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="B531" t="n">
@@ -25408,7 +25420,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="B532" t="n">
@@ -25455,7 +25467,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B533" t="n">
@@ -25502,7 +25514,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B534" t="n">
@@ -25549,7 +25561,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="B535" t="n">
@@ -25596,7 +25608,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B536" t="n">
@@ -25643,7 +25655,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B537" t="n">
@@ -25690,7 +25702,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="B538" t="n">
@@ -25737,7 +25749,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="B539" t="n">
@@ -25784,7 +25796,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="B540" t="n">
@@ -25831,7 +25843,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="B541" t="n">
@@ -25878,7 +25890,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B542" t="n">
@@ -25925,7 +25937,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B543" t="n">
@@ -25972,7 +25984,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="B544" t="n">
@@ -26019,7 +26031,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45609</v>
       </c>
       <c r="B545" t="n">
@@ -26066,7 +26078,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45610</v>
       </c>
       <c r="B546" t="n">
@@ -26113,7 +26125,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B547" t="n">
@@ -26160,7 +26172,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45614</v>
       </c>
       <c r="B548" t="n">
@@ -26207,7 +26219,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="B549" t="n">
@@ -26254,7 +26266,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="B550" t="n">
@@ -26301,7 +26313,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="B551" t="n">
@@ -26348,7 +26360,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B552" t="n">
@@ -26395,7 +26407,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45621</v>
       </c>
       <c r="B553" t="n">
@@ -26442,7 +26454,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45622</v>
       </c>
       <c r="B554" t="n">
@@ -26489,7 +26501,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="B555" t="n">
@@ -26536,7 +26548,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45624</v>
       </c>
       <c r="B556" t="n">
@@ -26583,7 +26595,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B557" t="n">
@@ -26630,7 +26642,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45628</v>
       </c>
       <c r="B558" t="n">
@@ -26677,7 +26689,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45629</v>
       </c>
       <c r="B559" t="n">
@@ -26724,7 +26736,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="B560" t="n">
@@ -26771,7 +26783,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45631</v>
       </c>
       <c r="B561" t="n">
@@ -26818,7 +26830,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B562" t="n">
@@ -26865,7 +26877,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45635</v>
       </c>
       <c r="B563" t="n">
@@ -26912,7 +26924,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="B564" t="n">
@@ -26959,7 +26971,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45637</v>
       </c>
       <c r="B565" t="n">
@@ -27006,7 +27018,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45638</v>
       </c>
       <c r="B566" t="n">
@@ -27053,7 +27065,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B567" t="n">
@@ -27100,7 +27112,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45642</v>
       </c>
       <c r="B568" t="n">
@@ -27147,7 +27159,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45643</v>
       </c>
       <c r="B569" t="n">
@@ -27194,7 +27206,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45644</v>
       </c>
       <c r="B570" t="n">
@@ -27241,7 +27253,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="B571" t="n">
@@ -27288,7 +27300,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B572" t="n">
@@ -27335,7 +27347,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>45649</v>
       </c>
       <c r="B573" t="n">
@@ -27382,7 +27394,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>45650</v>
       </c>
       <c r="B574" t="n">
@@ -27429,7 +27441,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>45651</v>
       </c>
       <c r="B575" t="n">
@@ -27476,7 +27488,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>45652</v>
       </c>
       <c r="B576" t="n">
@@ -27523,7 +27535,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B577" t="n">
@@ -27570,7 +27582,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>45656</v>
       </c>
       <c r="B578" t="n">
@@ -27617,7 +27629,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B579" t="n">
@@ -27664,7 +27676,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>45659</v>
       </c>
       <c r="B580" t="n">
@@ -27711,7 +27723,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B581" t="n">
@@ -27758,7 +27770,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B582" t="n">
@@ -27805,7 +27817,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="B583" t="n">
@@ -27852,7 +27864,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>45665</v>
       </c>
       <c r="B584" t="n">
@@ -27899,7 +27911,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="B585" t="n">
@@ -27946,7 +27958,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B586" t="n">
@@ -27993,7 +28005,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="B587" t="n">
@@ -28040,7 +28052,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="B588" t="n">
@@ -28087,7 +28099,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="B589" t="n">
@@ -28134,7 +28146,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>45673</v>
       </c>
       <c r="B590" t="n">
@@ -28181,7 +28193,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B591" t="n">
@@ -28228,7 +28240,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B592" t="n">
@@ -28275,7 +28287,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="B593" t="n">
@@ -28322,7 +28334,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="B594" t="n">
@@ -28369,7 +28381,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="B595" t="n">
@@ -28416,7 +28428,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B596" t="n">
@@ -28463,7 +28475,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="B597" t="n">
@@ -28510,7 +28522,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="B598" t="n">
@@ -28557,7 +28569,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="B599" t="n">
@@ -28604,7 +28616,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="B600" t="n">
@@ -28651,7 +28663,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B601" t="n">
@@ -28698,7 +28710,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="B602" t="n">
@@ -28745,7 +28757,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="B603" t="n">
@@ -28792,7 +28804,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="B604" t="n">
@@ -28839,7 +28851,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="B605" t="n">
@@ -28886,7 +28898,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B606" t="n">
@@ -28933,7 +28945,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B607" t="n">
@@ -28980,7 +28992,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="B608" t="n">
@@ -29027,7 +29039,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="B609" t="n">
@@ -29074,7 +29086,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="1" t="n">
+      <c r="A610" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="B610" t="n">
@@ -29121,7 +29133,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="1" t="n">
+      <c r="A611" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B611" t="n">
@@ -29168,7 +29180,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="1" t="n">
+      <c r="A612" s="2" t="n">
         <v>45705</v>
       </c>
       <c r="B612" t="n">
@@ -29215,7 +29227,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="1" t="n">
+      <c r="A613" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="B613" t="n">
@@ -29262,7 +29274,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="1" t="n">
+      <c r="A614" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="B614" t="n">
@@ -29309,7 +29321,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="1" t="n">
+      <c r="A615" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="B615" t="n">
@@ -29356,7 +29368,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="1" t="n">
+      <c r="A616" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B616" t="n">
@@ -29403,7 +29415,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="1" t="n">
+      <c r="A617" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="B617" t="n">
@@ -29450,7 +29462,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="1" t="n">
+      <c r="A618" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="B618" t="n">
@@ -29497,7 +29509,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="1" t="n">
+      <c r="A619" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="B619" t="n">
@@ -29544,7 +29556,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="1" t="n">
+      <c r="A620" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="B620" t="n">
@@ -29591,7 +29603,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="1" t="n">
+      <c r="A621" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B621" t="n">
@@ -29638,7 +29650,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="1" t="n">
+      <c r="A622" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="B622" t="n">
@@ -29685,7 +29697,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="1" t="n">
+      <c r="A623" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="B623" t="n">
@@ -29732,7 +29744,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="1" t="n">
+      <c r="A624" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B624" t="n">
@@ -29779,7 +29791,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="1" t="n">
+      <c r="A625" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="B625" t="n">
@@ -29826,7 +29838,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="1" t="n">
+      <c r="A626" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B626" t="n">
@@ -29873,7 +29885,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="1" t="n">
+      <c r="A627" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="B627" t="n">
@@ -29920,7 +29932,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="1" t="n">
+      <c r="A628" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="B628" t="n">
@@ -29967,7 +29979,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="1" t="n">
+      <c r="A629" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="B629" t="n">
@@ -30014,7 +30026,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="1" t="n">
+      <c r="A630" s="2" t="n">
         <v>45729</v>
       </c>
       <c r="B630" t="n">
@@ -30061,7 +30073,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="1" t="n">
+      <c r="A631" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B631" t="n">
@@ -30108,7 +30120,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="1" t="n">
+      <c r="A632" s="2" t="n">
         <v>45733</v>
       </c>
       <c r="B632" t="n">
@@ -30155,7 +30167,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="1" t="n">
+      <c r="A633" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="B633" t="n">
@@ -30202,7 +30214,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="1" t="n">
+      <c r="A634" s="2" t="n">
         <v>45735</v>
       </c>
       <c r="B634" t="n">
@@ -30249,7 +30261,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="1" t="n">
+      <c r="A635" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="B635" t="n">
@@ -30296,7 +30308,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="1" t="n">
+      <c r="A636" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B636" t="n">
@@ -30343,7 +30355,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="1" t="n">
+      <c r="A637" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="B637" t="n">
@@ -30390,7 +30402,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="1" t="n">
+      <c r="A638" s="2" t="n">
         <v>45741</v>
       </c>
       <c r="B638" t="n">
@@ -30437,7 +30449,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="1" t="n">
+      <c r="A639" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="B639" t="n">
@@ -30484,7 +30496,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="1" t="n">
+      <c r="A640" s="2" t="n">
         <v>45743</v>
       </c>
       <c r="B640" t="n">
@@ -30531,7 +30543,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="1" t="n">
+      <c r="A641" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B641" t="n">
@@ -30578,7 +30590,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="1" t="n">
+      <c r="A642" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="B642" t="n">
@@ -30625,7 +30637,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="1" t="n">
+      <c r="A643" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="B643" t="n">
@@ -30672,7 +30684,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="1" t="n">
+      <c r="A644" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B644" t="n">
@@ -30719,7 +30731,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="1" t="n">
+      <c r="A645" s="2" t="n">
         <v>45754</v>
       </c>
       <c r="B645" t="n">
@@ -30766,7 +30778,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="1" t="n">
+      <c r="A646" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="B646" t="n">
@@ -30813,7 +30825,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="1" t="n">
+      <c r="A647" s="2" t="n">
         <v>45756</v>
       </c>
       <c r="B647" t="n">
@@ -30860,7 +30872,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="1" t="n">
+      <c r="A648" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="B648" t="n">
@@ -30907,7 +30919,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="1" t="n">
+      <c r="A649" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B649" t="n">
@@ -30954,7 +30966,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="1" t="n">
+      <c r="A650" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B650" t="n">
@@ -31001,7 +31013,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="1" t="n">
+      <c r="A651" s="2" t="n">
         <v>45762</v>
       </c>
       <c r="B651" t="n">
@@ -31048,7 +31060,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="1" t="n">
+      <c r="A652" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="B652" t="n">
@@ -31095,7 +31107,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="1" t="n">
+      <c r="A653" s="2" t="n">
         <v>45764</v>
       </c>
       <c r="B653" t="n">
@@ -31142,7 +31154,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="1" t="n">
+      <c r="A654" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B654" t="n">
@@ -31189,7 +31201,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="1" t="n">
+      <c r="A655" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B655" t="n">
@@ -31236,7 +31248,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="1" t="n">
+      <c r="A656" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="B656" t="n">
@@ -31283,7 +31295,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" s="1" t="n">
+      <c r="A657" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="B657" t="n">
@@ -31330,7 +31342,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" s="1" t="n">
+      <c r="A658" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B658" t="n">
@@ -31377,7 +31389,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="1" t="n">
+      <c r="A659" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="B659" t="n">
@@ -31424,7 +31436,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" s="1" t="n">
+      <c r="A660" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="B660" t="n">
@@ -31471,7 +31483,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" s="1" t="n">
+      <c r="A661" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B661" t="n">
@@ -31518,7 +31530,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="1" t="n">
+      <c r="A662" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B662" t="n">
@@ -31565,7 +31577,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" s="1" t="n">
+      <c r="A663" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="B663" t="n">
@@ -31612,7 +31624,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="1" t="n">
+      <c r="A664" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="B664" t="n">
@@ -31659,7 +31671,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" s="1" t="n">
+      <c r="A665" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="B665" t="n">
@@ -31706,7 +31718,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="1" t="n">
+      <c r="A666" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="B666" t="n">
@@ -31753,7 +31765,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" s="1" t="n">
+      <c r="A667" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B667" t="n">
@@ -31800,7 +31812,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" s="1" t="n">
+      <c r="A668" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="B668" t="n">
@@ -31847,7 +31859,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="1" t="n">
+      <c r="A669" s="2" t="n">
         <v>45790</v>
       </c>
       <c r="B669" t="n">
@@ -31894,7 +31906,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" s="1" t="n">
+      <c r="A670" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="B670" t="n">
@@ -31941,7 +31953,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" s="1" t="n">
+      <c r="A671" s="2" t="n">
         <v>45792</v>
       </c>
       <c r="B671" t="n">
@@ -31988,7 +32000,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" s="1" t="n">
+      <c r="A672" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B672" t="n">
@@ -32035,7 +32047,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="1" t="n">
+      <c r="A673" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="B673" t="n">
@@ -32082,7 +32094,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" s="1" t="n">
+      <c r="A674" s="2" t="n">
         <v>45798</v>
       </c>
       <c r="B674" t="n">
@@ -32129,7 +32141,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" s="1" t="n">
+      <c r="A675" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="B675" t="n">
@@ -32176,7 +32188,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="1" t="n">
+      <c r="A676" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B676" t="n">
@@ -32223,7 +32235,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" s="1" t="n">
+      <c r="A677" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="B677" t="n">
@@ -32270,7 +32282,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" s="1" t="n">
+      <c r="A678" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="B678" t="n">
@@ -32317,7 +32329,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" s="1" t="n">
+      <c r="A679" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="B679" t="n">
@@ -32364,7 +32376,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" s="1" t="n">
+      <c r="A680" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="B680" t="n">
@@ -32411,7 +32423,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="1" t="n">
+      <c r="A681" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B681" t="n">
@@ -32458,7 +32470,7 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" s="1" t="n">
+      <c r="A682" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B682" t="n">
@@ -32505,7 +32517,7 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" s="1" t="n">
+      <c r="A683" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B683" t="n">
@@ -32552,7 +32564,7 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" s="1" t="n">
+      <c r="A684" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="B684" t="n">
@@ -32599,7 +32611,7 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" s="1" t="n">
+      <c r="A685" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B685" t="n">
@@ -32646,7 +32658,7 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" s="1" t="n">
+      <c r="A686" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="B686" t="n">
@@ -32693,7 +32705,7 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" s="1" t="n">
+      <c r="A687" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B687" t="n">
@@ -32740,7 +32752,7 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="1" t="n">
+      <c r="A688" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B688" t="n">
@@ -32787,7 +32799,7 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" s="1" t="n">
+      <c r="A689" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B689" t="n">
@@ -32834,7 +32846,7 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" s="1" t="n">
+      <c r="A690" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B690" t="n">
@@ -32881,7 +32893,7 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" s="1" t="n">
+      <c r="A691" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B691" t="n">
@@ -32928,7 +32940,7 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" s="1" t="n">
+      <c r="A692" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B692" t="n">
@@ -32975,7 +32987,7 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" s="1" t="n">
+      <c r="A693" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B693" t="n">
@@ -33022,7 +33034,7 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" s="1" t="n">
+      <c r="A694" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B694" t="n">
@@ -33069,7 +33081,7 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" s="1" t="n">
+      <c r="A695" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B695" t="n">
@@ -33116,7 +33128,7 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" s="1" t="n">
+      <c r="A696" s="2" t="n">
         <v>45832</v>
       </c>
       <c r="B696" t="n">
@@ -33163,7 +33175,7 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" s="1" t="n">
+      <c r="A697" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B697" t="n">
@@ -33210,7 +33222,7 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" s="1" t="n">
+      <c r="A698" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B698" t="n">
@@ -33257,7 +33269,7 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" s="1" t="n">
+      <c r="A699" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B699" t="n">
@@ -33304,7 +33316,7 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" s="1" t="n">
+      <c r="A700" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B700" t="n">
@@ -33351,7 +33363,7 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" s="1" t="n">
+      <c r="A701" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B701" t="n">
@@ -33398,7 +33410,7 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" s="1" t="n">
+      <c r="A702" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B702" t="n">
@@ -33445,7 +33457,7 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" s="1" t="n">
+      <c r="A703" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B703" t="n">
@@ -33492,7 +33504,7 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" s="1" t="n">
+      <c r="A704" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B704" t="n">
@@ -33539,7 +33551,7 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" s="1" t="n">
+      <c r="A705" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B705" t="n">
@@ -33586,7 +33598,7 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" s="1" t="n">
+      <c r="A706" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="B706" t="n">
@@ -33633,7 +33645,7 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" s="1" t="n">
+      <c r="A707" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B707" t="n">
@@ -33680,7 +33692,7 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" s="1" t="n">
+      <c r="A708" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B708" t="n">
@@ -33727,7 +33739,7 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" s="1" t="n">
+      <c r="A709" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B709" t="n">
@@ -33774,7 +33786,7 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" s="1" t="n">
+      <c r="A710" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B710" t="n">
@@ -33821,7 +33833,7 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" s="1" t="n">
+      <c r="A711" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="B711" t="n">
@@ -33868,7 +33880,7 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" s="1" t="n">
+      <c r="A712" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="B712" t="n">
@@ -33915,7 +33927,7 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" s="1" t="n">
+      <c r="A713" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B713" t="n">
@@ -33962,7 +33974,7 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" s="1" t="n">
+      <c r="A714" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B714" t="n">
@@ -34009,7 +34021,7 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" s="1" t="n">
+      <c r="A715" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B715" t="n">
@@ -34056,7 +34068,7 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" s="1" t="n">
+      <c r="A716" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B716" t="n">
@@ -34103,7 +34115,7 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" s="1" t="n">
+      <c r="A717" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="B717" t="n">
@@ -34150,7 +34162,7 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" s="1" t="n">
+      <c r="A718" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B718" t="n">
@@ -34197,7 +34209,7 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" s="1" t="n">
+      <c r="A719" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B719" t="n">
@@ -34244,7 +34256,7 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" s="1" t="n">
+      <c r="A720" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="B720" t="n">
@@ -34291,7 +34303,7 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" s="1" t="n">
+      <c r="A721" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="B721" t="n">
@@ -34338,7 +34350,7 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" s="1" t="n">
+      <c r="A722" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B722" t="n">
@@ -34385,7 +34397,7 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" s="1" t="n">
+      <c r="A723" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B723" t="n">
@@ -34432,7 +34444,7 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" s="1" t="n">
+      <c r="A724" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="B724" t="n">
@@ -34479,7 +34491,7 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" s="1" t="n">
+      <c r="A725" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="B725" t="n">
@@ -34526,7 +34538,7 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" s="1" t="n">
+      <c r="A726" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="B726" t="n">
@@ -34573,7 +34585,7 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" s="1" t="n">
+      <c r="A727" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="B727" t="n">
@@ -34620,7 +34632,7 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" s="1" t="n">
+      <c r="A728" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B728" t="n">
@@ -34667,7 +34679,7 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" s="1" t="n">
+      <c r="A729" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B729" t="n">
@@ -34714,7 +34726,7 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" s="1" t="n">
+      <c r="A730" s="2" t="n">
         <v>45881</v>
       </c>
       <c r="B730" t="n">
@@ -34761,7 +34773,7 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" s="1" t="n">
+      <c r="A731" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="B731" t="n">
@@ -34808,7 +34820,7 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" s="1" t="n">
+      <c r="A732" s="2" t="n">
         <v>45883</v>
       </c>
       <c r="B732" t="n">
@@ -34855,7 +34867,7 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" s="1" t="n">
+      <c r="A733" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B733" t="n">
@@ -34902,7 +34914,7 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" s="1" t="n">
+      <c r="A734" s="2" t="n">
         <v>45887</v>
       </c>
       <c r="B734" t="n">
@@ -34949,7 +34961,7 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" s="1" t="n">
+      <c r="A735" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="B735" t="n">
@@ -34996,7 +35008,7 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" s="1" t="n">
+      <c r="A736" s="2" t="n">
         <v>45889</v>
       </c>
       <c r="B736" t="n">
@@ -35043,7 +35055,7 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" s="1" t="n">
+      <c r="A737" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B737" t="n">
@@ -35090,7 +35102,7 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" s="1" t="n">
+      <c r="A738" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B738" t="n">
@@ -35137,7 +35149,7 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="1" t="n">
+      <c r="A739" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B739" t="n">
@@ -35184,7 +35196,7 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" s="1" t="n">
+      <c r="A740" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="B740" t="n">
@@ -35231,7 +35243,7 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" s="1" t="n">
+      <c r="A741" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="B741" t="n">
@@ -35278,7 +35290,7 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" s="1" t="n">
+      <c r="A742" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="B742" t="n">
@@ -35325,7 +35337,7 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" s="1" t="n">
+      <c r="A743" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B743" t="n">
@@ -35372,7 +35384,7 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" s="1" t="n">
+      <c r="A744" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B744" t="n">
@@ -35419,7 +35431,7 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" s="1" t="n">
+      <c r="A745" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="B745" t="n">
@@ -35466,7 +35478,7 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="1" t="n">
+      <c r="A746" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="B746" t="n">
@@ -35513,7 +35525,7 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" s="1" t="n">
+      <c r="A747" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="B747" t="n">
@@ -35560,7 +35572,7 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" s="1" t="n">
+      <c r="A748" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B748" t="n">
@@ -35607,7 +35619,7 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" s="1" t="n">
+      <c r="A749" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="B749" t="n">
@@ -35654,7 +35666,7 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" s="1" t="n">
+      <c r="A750" s="2" t="n">
         <v>45909</v>
       </c>
       <c r="B750" t="n">
@@ -35701,7 +35713,7 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" s="1" t="n">
+      <c r="A751" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="B751" t="n">
@@ -35748,7 +35760,7 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" s="1" t="n">
+      <c r="A752" s="2" t="n">
         <v>45911</v>
       </c>
       <c r="B752" t="n">
@@ -35795,7 +35807,7 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" s="1" t="n">
+      <c r="A753" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B753" t="n">
@@ -35842,7 +35854,7 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" s="1" t="n">
+      <c r="A754" s="2" t="n">
         <v>45915</v>
       </c>
       <c r="B754" t="n">
@@ -35889,7 +35901,7 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" s="1" t="n">
+      <c r="A755" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B755" t="n">
@@ -35936,7 +35948,7 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" s="1" t="n">
+      <c r="A756" s="2" t="n">
         <v>45917</v>
       </c>
       <c r="B756" t="n">
@@ -35983,7 +35995,7 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" s="1" t="n">
+      <c r="A757" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="B757" t="n">
@@ -36030,7 +36042,7 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" s="1" t="n">
+      <c r="A758" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B758" t="n">
@@ -36077,7 +36089,7 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" s="1" t="n">
+      <c r="A759" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B759" t="n">
@@ -36124,7 +36136,7 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" s="1" t="n">
+      <c r="A760" s="2" t="n">
         <v>45923</v>
       </c>
       <c r="B760" t="n">
@@ -36171,7 +36183,7 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" s="1" t="n">
+      <c r="A761" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="B761" t="n">
@@ -36218,7 +36230,7 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="1" t="n">
+      <c r="A762" s="2" t="n">
         <v>45925</v>
       </c>
       <c r="B762" t="n">
@@ -36265,7 +36277,7 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" s="1" t="n">
+      <c r="A763" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B763" t="n">
@@ -36312,7 +36324,7 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" s="1" t="n">
+      <c r="A764" s="2" t="n">
         <v>45929</v>
       </c>
       <c r="B764" t="n">
@@ -36359,7 +36371,7 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" s="1" t="n">
+      <c r="A765" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B765" t="n">
@@ -36406,7 +36418,7 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" s="1" t="n">
+      <c r="A766" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B766" t="n">
@@ -36453,7 +36465,7 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" s="1" t="n">
+      <c r="A767" s="2" t="n">
         <v>45932</v>
       </c>
       <c r="B767" t="n">
@@ -36500,7 +36512,7 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" s="1" t="n">
+      <c r="A768" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B768" t="n">
@@ -36547,7 +36559,7 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" s="1" t="n">
+      <c r="A769" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B769" t="n">
@@ -36594,7 +36606,7 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" s="1" t="n">
+      <c r="A770" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="B770" t="n">
@@ -36641,7 +36653,7 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" s="1" t="n">
+      <c r="A771" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="B771" t="n">
@@ -36688,7 +36700,7 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" s="1" t="n">
+      <c r="A772" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="B772" t="n">
@@ -36735,7 +36747,7 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" s="1" t="n">
+      <c r="A773" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B773" t="n">
@@ -36782,7 +36794,7 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" s="1" t="n">
+      <c r="A774" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="B774" t="n">
@@ -36829,7 +36841,7 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" s="1" t="n">
+      <c r="A775" s="2" t="n">
         <v>45944</v>
       </c>
       <c r="B775" t="n">
@@ -36876,7 +36888,7 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" s="1" t="n">
+      <c r="A776" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="B776" t="n">
@@ -36923,7 +36935,7 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" s="1" t="n">
+      <c r="A777" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="B777" t="n">
@@ -36970,7 +36982,7 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" s="1" t="n">
+      <c r="A778" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B778" t="n">
@@ -37017,7 +37029,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="1" t="n">
+      <c r="A779" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B779" t="n">
@@ -37064,7 +37076,7 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" s="1" t="n">
+      <c r="A780" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="B780" t="n">
@@ -37111,7 +37123,7 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" s="1" t="n">
+      <c r="A781" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="B781" t="n">
@@ -37158,7 +37170,7 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="1" t="n">
+      <c r="A782" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="B782" t="n">
@@ -37205,7 +37217,7 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" s="1" t="n">
+      <c r="A783" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B783" t="n">
@@ -37252,7 +37264,7 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" s="1" t="n">
+      <c r="A784" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B784" t="n">
@@ -37299,7 +37311,7 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" s="1" t="n">
+      <c r="A785" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="B785" t="n">
@@ -37346,7 +37358,7 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" s="1" t="n">
+      <c r="A786" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B786" t="n">
@@ -37393,7 +37405,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" s="1" t="n">
+      <c r="A787" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B787" t="n">
@@ -37440,7 +37452,7 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" s="1" t="n">
+      <c r="A788" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="B788" t="n">
@@ -37487,7 +37499,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" s="1" t="n">
+      <c r="A789" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="B789" t="n">
@@ -37534,7 +37546,7 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" s="1" t="n">
+      <c r="A790" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="B790" t="n">
@@ -37581,7 +37593,7 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="1" t="n">
+      <c r="A791" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="B791" t="n">
@@ -37628,7 +37640,7 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" s="1" t="n">
+      <c r="A792" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B792" t="n">
@@ -37675,7 +37687,7 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" s="1" t="n">
+      <c r="A793" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="B793" t="n">
@@ -37722,7 +37734,7 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" s="1" t="n">
+      <c r="A794" s="2" t="n">
         <v>45972</v>
       </c>
       <c r="B794" t="n">
@@ -37769,7 +37781,7 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" s="1" t="n">
+      <c r="A795" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="B795" t="n">
@@ -37816,7 +37828,7 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" s="1" t="n">
+      <c r="A796" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="B796" t="n">
@@ -37863,7 +37875,7 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" s="1" t="n">
+      <c r="A797" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B797" t="n">
@@ -37910,7 +37922,7 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" s="1" t="n">
+      <c r="A798" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B798" t="n">
@@ -37957,7 +37969,7 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" s="1" t="n">
+      <c r="A799" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="B799" t="n">
@@ -38004,7 +38016,7 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" s="1" t="n">
+      <c r="A800" s="2" t="n">
         <v>45980</v>
       </c>
       <c r="B800" t="n">
@@ -38051,7 +38063,7 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" s="1" t="n">
+      <c r="A801" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="B801" t="n">
@@ -38098,7 +38110,7 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" s="1" t="n">
+      <c r="A802" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B802" t="n">
@@ -38145,7 +38157,7 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" s="1" t="n">
+      <c r="A803" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="B803" t="n">
@@ -38192,7 +38204,7 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" s="1" t="n">
+      <c r="A804" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="B804" t="n">
@@ -38239,7 +38251,7 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="1" t="n">
+      <c r="A805" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="B805" t="n">
@@ -38286,7 +38298,7 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" s="1" t="n">
+      <c r="A806" s="2" t="n">
         <v>45988</v>
       </c>
       <c r="B806" t="n">
@@ -38333,7 +38345,7 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" s="1" t="n">
+      <c r="A807" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B807" t="n">
@@ -38380,7 +38392,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" s="1" t="n">
+      <c r="A808" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B808" t="n">
@@ -38427,7 +38439,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" s="1" t="n">
+      <c r="A809" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="B809" t="n">
@@ -38474,7 +38486,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" s="1" t="n">
+      <c r="A810" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="B810" t="n">
@@ -38521,7 +38533,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" s="1" t="n">
+      <c r="A811" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="B811" t="n">
@@ -38568,7 +38580,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" s="1" t="n">
+      <c r="A812" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B812" t="n">
@@ -38615,7 +38627,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" s="1" t="n">
+      <c r="A813" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B813" t="n">
@@ -38662,7 +38674,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" s="1" t="n">
+      <c r="A814" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="B814" t="n">
@@ -38709,7 +38721,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" s="1" t="n">
+      <c r="A815" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="B815" t="n">
@@ -38756,7 +38768,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" s="1" t="n">
+      <c r="A816" s="2" t="n">
         <v>46002</v>
       </c>
       <c r="B816" t="n">
@@ -38803,7 +38815,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" s="1" t="n">
+      <c r="A817" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B817" t="n">
@@ -38850,7 +38862,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" s="1" t="n">
+      <c r="A818" s="2" t="n">
         <v>46006</v>
       </c>
       <c r="B818" t="n">
@@ -38897,7 +38909,7 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="1" t="n">
+      <c r="A819" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="B819" t="n">
@@ -38944,7 +38956,7 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" s="1" t="n">
+      <c r="A820" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="B820" t="n">
@@ -38991,7 +39003,7 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" s="1" t="n">
+      <c r="A821" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="B821" t="n">
@@ -39038,7 +39050,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" s="1" t="n">
+      <c r="A822" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B822" t="n">
@@ -39085,7 +39097,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" s="1" t="n">
+      <c r="A823" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B823" t="n">
@@ -39132,7 +39144,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" s="1" t="n">
+      <c r="A824" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="B824" t="n">
@@ -39179,7 +39191,7 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" s="1" t="n">
+      <c r="A825" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="B825" t="n">
@@ -39226,7 +39238,7 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" s="1" t="n">
+      <c r="A826" s="2" t="n">
         <v>46016</v>
       </c>
       <c r="B826" t="n">
@@ -39273,7 +39285,7 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" s="1" t="n">
+      <c r="A827" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B827" t="n">
@@ -39320,7 +39332,7 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="1" t="n">
+      <c r="A828" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B828" t="n">
@@ -39367,7 +39379,7 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" s="1" t="n">
+      <c r="A829" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="B829" t="n">
@@ -39414,7 +39426,7 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" s="1" t="n">
+      <c r="A830" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B830" t="n">
@@ -39461,7 +39473,7 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" s="1" t="n">
+      <c r="A831" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B831" t="n">
@@ -39508,7 +39520,7 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" s="1" t="n">
+      <c r="A832" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="B832" t="n">
@@ -39555,7 +39567,7 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" s="1" t="n">
+      <c r="A833" s="2" t="n">
         <v>46028</v>
       </c>
       <c r="B833" t="n">
@@ -39602,7 +39614,7 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" s="1" t="n">
+      <c r="A834" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="B834" t="n">
@@ -39649,7 +39661,7 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" s="1" t="n">
+      <c r="A835" s="2" t="n">
         <v>46030</v>
       </c>
       <c r="B835" t="n">
@@ -39696,7 +39708,7 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" s="1" t="n">
+      <c r="A836" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B836" t="n">
@@ -39743,7 +39755,7 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" s="1" t="n">
+      <c r="A837" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="B837" t="n">
@@ -39790,7 +39802,7 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" s="1" t="n">
+      <c r="A838" s="2" t="n">
         <v>46035</v>
       </c>
       <c r="B838" t="n">
@@ -39837,7 +39849,7 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" s="1" t="n">
+      <c r="A839" s="2" t="n">
         <v>46036</v>
       </c>
       <c r="B839" t="n">
@@ -39884,7 +39896,7 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" s="1" t="n">
+      <c r="A840" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="B840" t="n">
@@ -39931,7 +39943,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" s="1" t="n">
+      <c r="A841" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B841" t="n">
@@ -39978,7 +39990,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" s="1" t="n">
+      <c r="A842" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="B842" t="n">
@@ -40025,7 +40037,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" s="1" t="n">
+      <c r="A843" s="2" t="n">
         <v>46042</v>
       </c>
       <c r="B843" t="n">
@@ -40072,7 +40084,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" s="1" t="n">
+      <c r="A844" s="2" t="n">
         <v>46043</v>
       </c>
       <c r="B844" t="n">
@@ -40119,7 +40131,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" s="1" t="n">
+      <c r="A845" s="2" t="n">
         <v>46044</v>
       </c>
       <c r="B845" t="n">
@@ -40166,7 +40178,7 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" s="1" t="n">
+      <c r="A846" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B846" t="n">
@@ -40213,7 +40225,7 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" s="1" t="n">
+      <c r="A847" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="B847" t="n">
@@ -40260,7 +40272,7 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" s="1" t="n">
+      <c r="A848" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="B848" t="n">
@@ -40307,7 +40319,7 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" s="1" t="n">
+      <c r="A849" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="B849" t="n">
@@ -40354,7 +40366,7 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" s="1" t="n">
+      <c r="A850" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="B850" t="n">
@@ -40401,7 +40413,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" s="1" t="n">
+      <c r="A851" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B851" t="n">
@@ -40448,7 +40460,7 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" s="1" t="n">
+      <c r="A852" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B852" t="n">
@@ -40495,7 +40507,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" s="1" t="n">
+      <c r="A853" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="B853" t="n">
@@ -40542,7 +40554,7 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" s="1" t="n">
+      <c r="A854" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="B854" t="n">
@@ -40589,7 +40601,7 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" s="1" t="n">
+      <c r="A855" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="B855" t="n">
@@ -40636,7 +40648,7 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" s="1" t="n">
+      <c r="A856" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B856" t="n">
@@ -40683,7 +40695,7 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" s="1" t="n">
+      <c r="A857" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B857" t="n">
@@ -40730,7 +40742,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" s="1" t="n">
+      <c r="A858" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="B858" t="n">
@@ -40777,7 +40789,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" s="1" t="n">
+      <c r="A859" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="B859" t="n">
@@ -40824,7 +40836,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" s="1" t="n">
+      <c r="A860" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="B860" t="n">
@@ -40871,7 +40883,7 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" s="1" t="n">
+      <c r="A861" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B861" t="n">
@@ -40918,7 +40930,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" s="1" t="n">
+      <c r="A862" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B862" t="n">
@@ -40965,7 +40977,7 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" s="1" t="n">
+      <c r="A863" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="B863" t="n">
@@ -41012,7 +41024,7 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" s="1" t="n">
+      <c r="A864" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="B864" t="n">
@@ -41059,7 +41071,7 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" s="1" t="n">
+      <c r="A865" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="B865" t="n">
@@ -41106,7 +41118,7 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" s="1" t="n">
+      <c r="A866" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B866" t="n">
@@ -41153,7 +41165,7 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" s="1" t="n">
+      <c r="A867" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="B867" t="n">
@@ -41200,7 +41212,7 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" s="1" t="n">
+      <c r="A868" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="B868" t="n">
@@ -41247,7 +41259,7 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" s="1" t="n">
+      <c r="A869" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="B869" t="n">
@@ -41294,7 +41306,7 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" s="1" t="n">
+      <c r="A870" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="B870" t="n">
@@ -41341,7 +41353,7 @@
       </c>
     </row>
     <row r="871">
-      <c r="A871" s="1" t="n">
+      <c r="A871" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B871" t="n">
@@ -41388,7 +41400,7 @@
       </c>
     </row>
     <row r="872">
-      <c r="A872" s="1" t="n">
+      <c r="A872" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="B872" t="n">
@@ -41435,7 +41447,7 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" s="1" t="n">
+      <c r="A873" s="2" t="n">
         <v>46084</v>
       </c>
       <c r="B873" t="n">
@@ -41482,7 +41494,7 @@
       </c>
     </row>
     <row r="874">
-      <c r="A874" s="1" t="n">
+      <c r="A874" s="2" t="n">
         <v>46085</v>
       </c>
       <c r="B874" t="n">
@@ -41529,7 +41541,7 @@
       </c>
     </row>
     <row r="875">
-      <c r="A875" s="1" t="n">
+      <c r="A875" s="2" t="n">
         <v>46086</v>
       </c>
       <c r="B875" t="n">
@@ -41576,7 +41588,7 @@
       </c>
     </row>
     <row r="876">
-      <c r="A876" s="1" t="n">
+      <c r="A876" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B876" t="n">
@@ -41623,7 +41635,7 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" s="1" t="n">
+      <c r="A877" s="2" t="n">
         <v>46090</v>
       </c>
       <c r="B877" t="n">
@@ -41670,7 +41682,7 @@
       </c>
     </row>
     <row r="878">
-      <c r="A878" s="1" t="n">
+      <c r="A878" s="2" t="n">
         <v>46091</v>
       </c>
       <c r="B878" t="n">
@@ -41717,7 +41729,7 @@
       </c>
     </row>
     <row r="879">
-      <c r="A879" s="1" t="n">
+      <c r="A879" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="B879" t="n">
@@ -41764,7 +41776,7 @@
       </c>
     </row>
     <row r="880">
-      <c r="A880" s="1" t="n">
+      <c r="A880" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B880" t="n">
@@ -41811,7 +41823,7 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" s="1" t="n">
+      <c r="A881" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B881" t="n">
@@ -41858,7 +41870,7 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" s="1" t="n">
+      <c r="A882" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B882" t="n">
@@ -41905,7 +41917,7 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" s="1" t="n">
+      <c r="A883" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B883" t="n">
@@ -41952,7 +41964,7 @@
       </c>
     </row>
     <row r="884">
-      <c r="A884" s="1" t="n">
+      <c r="A884" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="B884" t="n">
@@ -41999,7 +42011,7 @@
       </c>
     </row>
     <row r="885">
-      <c r="A885" s="1" t="n">
+      <c r="A885" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="B885" t="n">
@@ -42046,7 +42058,7 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" s="1" t="n">
+      <c r="A886" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="B886" t="n">
@@ -42093,7 +42105,7 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="1" t="n">
+      <c r="A887" s="2" t="n">
         <v>46105</v>
       </c>
       <c r="B887" t="n">
@@ -42140,7 +42152,7 @@
       </c>
     </row>
     <row r="888">
-      <c r="A888" s="1" t="n">
+      <c r="A888" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="B888" t="n">
@@ -42187,7 +42199,7 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" s="1" t="n">
+      <c r="A889" s="2" t="n">
         <v>46107</v>
       </c>
       <c r="B889" t="n">
@@ -42234,7 +42246,7 @@
       </c>
     </row>
     <row r="890">
-      <c r="A890" s="1" t="n">
+      <c r="A890" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B890" t="n">
@@ -42281,7 +42293,7 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" s="1" t="n">
+      <c r="A891" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="B891" t="n">
@@ -42328,7 +42340,7 @@
       </c>
     </row>
     <row r="892">
-      <c r="A892" s="1" t="n">
+      <c r="A892" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B892" t="n">
@@ -42375,7 +42387,7 @@
       </c>
     </row>
     <row r="893">
-      <c r="A893" s="1" t="n">
+      <c r="A893" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B893" t="n">
@@ -42422,7 +42434,7 @@
       </c>
     </row>
     <row r="894">
-      <c r="A894" s="1" t="n">
+      <c r="A894" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="B894" t="n">
@@ -42469,7 +42481,7 @@
       </c>
     </row>
     <row r="895">
-      <c r="A895" s="1" t="n">
+      <c r="A895" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B895" t="n">
@@ -42516,7 +42528,7 @@
       </c>
     </row>
     <row r="896">
-      <c r="A896" s="1" t="n">
+      <c r="A896" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="B896" t="n">
@@ -42563,7 +42575,7 @@
       </c>
     </row>
     <row r="897">
-      <c r="A897" s="1" t="n">
+      <c r="A897" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="B897" t="n">
@@ -42610,7 +42622,7 @@
       </c>
     </row>
     <row r="898">
-      <c r="A898" s="1" t="n">
+      <c r="A898" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="B898" t="n">
@@ -42657,7 +42669,7 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" s="1" t="n">
+      <c r="A899" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="B899" t="n">
@@ -42704,7 +42716,7 @@
       </c>
     </row>
     <row r="900">
-      <c r="A900" s="1" t="n">
+      <c r="A900" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B900" t="n">
@@ -42751,7 +42763,7 @@
       </c>
     </row>
     <row r="901">
-      <c r="A901" s="1" t="n">
+      <c r="A901" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="B901" t="n">
@@ -42798,7 +42810,7 @@
       </c>
     </row>
     <row r="902">
-      <c r="A902" s="1" t="n">
+      <c r="A902" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="B902" t="n">
@@ -42845,7 +42857,7 @@
       </c>
     </row>
     <row r="903">
-      <c r="A903" s="1" t="n">
+      <c r="A903" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="B903" t="n">
@@ -42892,7 +42904,7 @@
       </c>
     </row>
     <row r="904">
-      <c r="A904" s="1" t="n">
+      <c r="A904" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="B904" t="n">
@@ -42939,7 +42951,7 @@
       </c>
     </row>
     <row r="905">
-      <c r="A905" s="1" t="n">
+      <c r="A905" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B905" t="n">
@@ -42986,7 +42998,7 @@
       </c>
     </row>
     <row r="906">
-      <c r="A906" s="1" t="n">
+      <c r="A906" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="B906" t="n">
@@ -43033,7 +43045,7 @@
       </c>
     </row>
     <row r="907">
-      <c r="A907" s="1" t="n">
+      <c r="A907" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="B907" t="n">
@@ -43080,7 +43092,7 @@
       </c>
     </row>
     <row r="908">
-      <c r="A908" s="1" t="n">
+      <c r="A908" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="B908" t="n">
@@ -43127,7 +43139,7 @@
       </c>
     </row>
     <row r="909">
-      <c r="A909" s="1" t="n">
+      <c r="A909" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B909" t="n">
@@ -43174,7 +43186,7 @@
       </c>
     </row>
     <row r="910">
-      <c r="A910" s="1" t="n">
+      <c r="A910" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B910" t="n">
@@ -43221,7 +43233,7 @@
       </c>
     </row>
     <row r="911">
-      <c r="A911" s="1" t="n">
+      <c r="A911" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="B911" t="n">
@@ -43268,7 +43280,7 @@
       </c>
     </row>
     <row r="912">
-      <c r="A912" s="1" t="n">
+      <c r="A912" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="B912" t="n">
@@ -43315,7 +43327,7 @@
       </c>
     </row>
     <row r="913">
-      <c r="A913" s="1" t="n">
+      <c r="A913" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B913" t="n">
@@ -43362,7 +43374,7 @@
       </c>
     </row>
     <row r="914">
-      <c r="A914" s="1" t="n">
+      <c r="A914" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B914" t="n">
@@ -43409,7 +43421,7 @@
       </c>
     </row>
     <row r="915">
-      <c r="A915" s="1" t="n">
+      <c r="A915" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="B915" t="n">
@@ -43456,7 +43468,7 @@
       </c>
     </row>
     <row r="916">
-      <c r="A916" s="1" t="n">
+      <c r="A916" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="B916" t="n">
@@ -43503,7 +43515,7 @@
       </c>
     </row>
     <row r="917">
-      <c r="A917" s="1" t="n">
+      <c r="A917" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="B917" t="n">
@@ -43550,7 +43562,7 @@
       </c>
     </row>
     <row r="918">
-      <c r="A918" s="1" t="n">
+      <c r="A918" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B918" t="n">
@@ -43597,7 +43609,7 @@
       </c>
     </row>
     <row r="919">
-      <c r="A919" s="1" t="n">
+      <c r="A919" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B919" t="n">
@@ -43644,7 +43656,7 @@
       </c>
     </row>
     <row r="920">
-      <c r="A920" s="1" t="n">
+      <c r="A920" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="B920" t="n">
@@ -43691,7 +43703,7 @@
       </c>
     </row>
     <row r="921">
-      <c r="A921" s="1" t="n">
+      <c r="A921" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="B921" t="n">
@@ -43738,7 +43750,7 @@
       </c>
     </row>
     <row r="922">
-      <c r="A922" s="1" t="n">
+      <c r="A922" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="B922" t="n">
@@ -43785,7 +43797,7 @@
       </c>
     </row>
     <row r="923">
-      <c r="A923" s="1" t="n">
+      <c r="A923" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B923" t="n">
@@ -43832,7 +43844,7 @@
       </c>
     </row>
     <row r="924">
-      <c r="A924" s="1" t="n">
+      <c r="A924" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B924" t="n">
@@ -43879,7 +43891,7 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" s="1" t="n">
+      <c r="A925" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="B925" t="n">
@@ -43926,7 +43938,7 @@
       </c>
     </row>
     <row r="926">
-      <c r="A926" s="1" t="n">
+      <c r="A926" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B926" t="n">
@@ -43973,7 +43985,7 @@
       </c>
     </row>
     <row r="927">
-      <c r="A927" s="1" t="n">
+      <c r="A927" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B927" t="n">
@@ -44020,7 +44032,7 @@
       </c>
     </row>
     <row r="928">
-      <c r="A928" s="1" t="n">
+      <c r="A928" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="B928" t="n">
@@ -44067,7 +44079,7 @@
       </c>
     </row>
     <row r="929">
-      <c r="A929" s="1" t="n">
+      <c r="A929" s="2" t="n">
         <v>46168</v>
       </c>
       <c r="B929" t="n">
@@ -44114,7 +44126,7 @@
       </c>
     </row>
     <row r="930">
-      <c r="A930" s="1" t="n">
+      <c r="A930" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B930" t="n">
@@ -44161,7 +44173,7 @@
       </c>
     </row>
     <row r="931">
-      <c r="A931" s="1" t="n">
+      <c r="A931" s="2" t="n">
         <v>46175</v>
       </c>
       <c r="B931" t="n">
@@ -44208,7 +44220,7 @@
       </c>
     </row>
     <row r="932">
-      <c r="A932" s="1" t="n">
+      <c r="A932" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="B932" t="n">
@@ -44255,7 +44267,7 @@
       </c>
     </row>
     <row r="933">
-      <c r="A933" s="1" t="n">
+      <c r="A933" s="2" t="n">
         <v>46177</v>
       </c>
       <c r="B933" t="n">
@@ -44302,7 +44314,7 @@
       </c>
     </row>
     <row r="934">
-      <c r="A934" s="1" t="n">
+      <c r="A934" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B934" t="n">
@@ -44349,7 +44361,7 @@
       </c>
     </row>
     <row r="935">
-      <c r="A935" s="1" t="n">
+      <c r="A935" s="2" t="n">
         <v>46181</v>
       </c>
       <c r="B935" t="n">
@@ -44396,7 +44408,7 @@
       </c>
     </row>
     <row r="936">
-      <c r="A936" s="1" t="n">
+      <c r="A936" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="B936" t="n">
@@ -44443,7 +44455,7 @@
       </c>
     </row>
     <row r="937">
-      <c r="A937" s="1" t="n">
+      <c r="A937" s="2" t="n">
         <v>46183</v>
       </c>
       <c r="B937" t="n">
@@ -44490,7 +44502,7 @@
       </c>
     </row>
     <row r="938">
-      <c r="A938" s="1" t="n">
+      <c r="A938" s="2" t="n">
         <v>46184</v>
       </c>
       <c r="B938" t="n">
@@ -44537,7 +44549,7 @@
       </c>
     </row>
     <row r="939">
-      <c r="A939" s="1" t="n">
+      <c r="A939" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B939" t="n">
@@ -44584,7 +44596,7 @@
       </c>
     </row>
     <row r="940">
-      <c r="A940" s="1" t="n">
+      <c r="A940" s="2" t="n">
         <v>46188</v>
       </c>
       <c r="B940" t="n">
@@ -44631,7 +44643,7 @@
       </c>
     </row>
     <row r="941">
-      <c r="A941" s="1" t="n">
+      <c r="A941" s="2" t="n">
         <v>46189</v>
       </c>
       <c r="B941" t="n">
@@ -44678,7 +44690,7 @@
       </c>
     </row>
     <row r="942">
-      <c r="A942" s="1" t="n">
+      <c r="A942" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="B942" t="n">
@@ -44725,7 +44737,7 @@
       </c>
     </row>
     <row r="943">
-      <c r="A943" s="1" t="n">
+      <c r="A943" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="B943" t="n">
@@ -44772,7 +44784,7 @@
       </c>
     </row>
     <row r="944">
-      <c r="A944" s="1" t="n">
+      <c r="A944" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B944" t="n">
@@ -44819,7 +44831,7 @@
       </c>
     </row>
     <row r="945">
-      <c r="A945" s="1" t="n">
+      <c r="A945" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="B945" t="n">
@@ -44866,7 +44878,7 @@
       </c>
     </row>
     <row r="946">
-      <c r="A946" s="1" t="n">
+      <c r="A946" s="2" t="n">
         <v>46196</v>
       </c>
       <c r="B946" t="n">
@@ -44913,7 +44925,7 @@
       </c>
     </row>
     <row r="947">
-      <c r="A947" s="1" t="n">
+      <c r="A947" s="2" t="n">
         <v>46197</v>
       </c>
       <c r="B947" t="n">
@@ -44960,7 +44972,7 @@
       </c>
     </row>
     <row r="948">
-      <c r="A948" s="1" t="n">
+      <c r="A948" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="B948" t="n">
@@ -45007,7 +45019,7 @@
       </c>
     </row>
     <row r="949">
-      <c r="A949" s="1" t="n">
+      <c r="A949" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B949" t="n">
@@ -45054,7 +45066,7 @@
       </c>
     </row>
     <row r="950">
-      <c r="A950" s="1" t="n">
+      <c r="A950" s="2" t="n">
         <v>46202</v>
       </c>
       <c r="B950" t="n">
@@ -45101,7 +45113,7 @@
       </c>
     </row>
     <row r="951">
-      <c r="A951" s="1" t="n">
+      <c r="A951" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B951" t="n">
@@ -45148,7 +45160,7 @@
       </c>
     </row>
     <row r="952">
-      <c r="A952" s="1" t="n">
+      <c r="A952" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B952" t="n">
@@ -45195,7 +45207,7 @@
       </c>
     </row>
     <row r="953">
-      <c r="A953" s="1" t="n">
+      <c r="A953" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="B953" t="n">
@@ -45242,7 +45254,7 @@
       </c>
     </row>
     <row r="954">
-      <c r="A954" s="1" t="n">
+      <c r="A954" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B954" t="n">
@@ -45289,7 +45301,7 @@
       </c>
     </row>
     <row r="955">
-      <c r="A955" s="1" t="n">
+      <c r="A955" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="B955" t="n">
@@ -45336,7 +45348,7 @@
       </c>
     </row>
     <row r="956">
-      <c r="A956" s="1" t="n">
+      <c r="A956" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="B956" t="n">
@@ -45383,7 +45395,7 @@
       </c>
     </row>
     <row r="957">
-      <c r="A957" s="1" t="n">
+      <c r="A957" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="B957" t="n">
@@ -45430,7 +45442,7 @@
       </c>
     </row>
     <row r="958">
-      <c r="A958" s="1" t="n">
+      <c r="A958" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="B958" t="n">
@@ -45477,7 +45489,7 @@
       </c>
     </row>
     <row r="959">
-      <c r="A959" s="1" t="n">
+      <c r="A959" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B959" t="n">
@@ -45524,7 +45536,7 @@
       </c>
     </row>
     <row r="960">
-      <c r="A960" s="1" t="n">
+      <c r="A960" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="B960" t="n">
@@ -45571,7 +45583,7 @@
       </c>
     </row>
     <row r="961">
-      <c r="A961" s="1" t="n">
+      <c r="A961" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="B961" t="n">

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O961"/>
+  <dimension ref="A1:O962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45629,6 +45629,53 @@
         <v>4304109418</v>
       </c>
     </row>
+    <row r="962">
+      <c r="A962" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B962" t="n">
+        <v>46.9253</v>
+      </c>
+      <c r="C962" t="n">
+        <v>166219.719447718</v>
+      </c>
+      <c r="D962" t="n">
+        <v>14656.71816695898</v>
+      </c>
+      <c r="E962" t="n">
+        <v>6311.261813989468</v>
+      </c>
+      <c r="F962" t="n">
+        <v>93591.91591742622</v>
+      </c>
+      <c r="G962" t="n">
+        <v>150</v>
+      </c>
+      <c r="H962" t="n">
+        <v>2819.58958</v>
+      </c>
+      <c r="I962" t="n">
+        <v>-2669.58958</v>
+      </c>
+      <c r="J962" t="n">
+        <v>51659.82354934332</v>
+      </c>
+      <c r="K962" t="n">
+        <v>54329.41312934332</v>
+      </c>
+      <c r="L962" t="n">
+        <v>7799910201</v>
+      </c>
+      <c r="M962" t="n">
+        <v>687770897</v>
+      </c>
+      <c r="N962" t="n">
+        <v>296157854</v>
+      </c>
+      <c r="O962" t="n">
+        <v>4391828732</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>usdtry</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dis_varliklar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dis_yukumlulukler</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kamu_mevduati</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>banka_mevduati</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_alim</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>swap_satim</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>net_swap</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>net_rezerv_swap_dahil</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>net_rezerv_swap_haric</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>dis_varliklar_tl</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>dis_yukumlulukler_tl</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>kamu_mevduati_tl</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>banka_mevduati_tl</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44823</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44824</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44825</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44826</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44830</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44831</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44832</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44833</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44837</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44838</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44839</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44840</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44844</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44845</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44846</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44847</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44851</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44852</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44853</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44854</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44858</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44859</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44860</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44861</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44867</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44868</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44872</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44873</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44874</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44875</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44879</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44880</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44881</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44882</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44886</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44887</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44888</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44889</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44893</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44894</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44900</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44901</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44902</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44903</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44907</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44908</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44909</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44910</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44914</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44915</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44916</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44917</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44921</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44922</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44923</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44924</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44929</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44930</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44931</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44935</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44936</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44937</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44938</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44942</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44943</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44944</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44945</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44949</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44950</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44951</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44952</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44956</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44959</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44963</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44964</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44965</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44966</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44970</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44971</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44972</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44973</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44977</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44978</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44979</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44980</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44984</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44987</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44991</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44992</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44993</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44994</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44998</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44999</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>45000</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>45001</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>45005</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45006</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45007</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45008</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45012</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45013</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45014</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45015</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45019</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45020</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45021</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45022</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45026</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45027</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45029</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45033</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45034</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45036</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45040</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45041</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45043</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45048</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45049</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45050</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45054</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45056</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45057</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45061</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45062</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45063</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45064</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45068</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45069</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45070</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45075</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45076</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45082</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45083</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45089</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45090</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45091</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45092</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45096</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45097</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45099</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45110</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45111</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45112</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45113</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45119</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45120</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45124</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45125</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45126</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45127</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45131</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45132</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45134</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45140</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45141</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45145</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45146</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45147</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45148</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45152</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45153</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45154</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45159</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45160</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45161</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45162</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45166</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45167</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45173</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45174</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45175</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45176</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45180</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45181</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45182</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45183</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45187</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45188</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45189</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45190</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45194</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45195</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45196</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45197</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45201</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45202</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45203</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45204</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45208</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45209</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45210</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45211</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45215</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>45216</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>45217</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>45218</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>45222</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>45223</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>45224</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>45225</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>45271</v>
       </c>
       <c r="B315" t="n">
@@ -15268,7 +15256,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="B316" t="n">
@@ -15315,7 +15303,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>45273</v>
       </c>
       <c r="B317" t="n">
@@ -15362,7 +15350,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>45274</v>
       </c>
       <c r="B318" t="n">
@@ -15409,7 +15397,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B319" t="n">
@@ -15456,7 +15444,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>45278</v>
       </c>
       <c r="B320" t="n">
@@ -15503,7 +15491,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>45279</v>
       </c>
       <c r="B321" t="n">
@@ -15550,7 +15538,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>45280</v>
       </c>
       <c r="B322" t="n">
@@ -15597,7 +15585,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>45281</v>
       </c>
       <c r="B323" t="n">
@@ -15644,7 +15632,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B324" t="n">
@@ -15691,7 +15679,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>45285</v>
       </c>
       <c r="B325" t="n">
@@ -15738,7 +15726,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>45286</v>
       </c>
       <c r="B326" t="n">
@@ -15785,7 +15773,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>45287</v>
       </c>
       <c r="B327" t="n">
@@ -15832,7 +15820,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>45288</v>
       </c>
       <c r="B328" t="n">
@@ -15879,7 +15867,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B329" t="n">
@@ -15926,7 +15914,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B330" t="n">
@@ -15973,7 +15961,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>45294</v>
       </c>
       <c r="B331" t="n">
@@ -16020,7 +16008,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>45295</v>
       </c>
       <c r="B332" t="n">
@@ -16067,7 +16055,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B333" t="n">
@@ -16114,7 +16102,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>45299</v>
       </c>
       <c r="B334" t="n">
@@ -16161,7 +16149,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>45300</v>
       </c>
       <c r="B335" t="n">
@@ -16208,7 +16196,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>45301</v>
       </c>
       <c r="B336" t="n">
@@ -16255,7 +16243,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>45302</v>
       </c>
       <c r="B337" t="n">
@@ -16302,7 +16290,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B338" t="n">
@@ -16349,7 +16337,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="B339" t="n">
@@ -16396,7 +16384,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="B340" t="n">
@@ -16443,7 +16431,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="B341" t="n">
@@ -16490,7 +16478,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>45309</v>
       </c>
       <c r="B342" t="n">
@@ -16537,7 +16525,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B343" t="n">
@@ -16584,7 +16572,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="B344" t="n">
@@ -16631,7 +16619,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="B345" t="n">
@@ -16678,7 +16666,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="B346" t="n">
@@ -16725,7 +16713,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="B347" t="n">
@@ -16772,7 +16760,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B348" t="n">
@@ -16819,7 +16807,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="B349" t="n">
@@ -16866,7 +16854,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="B350" t="n">
@@ -16913,7 +16901,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B351" t="n">
@@ -16960,7 +16948,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B352" t="n">
@@ -17007,7 +16995,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B353" t="n">
@@ -17054,7 +17042,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="B354" t="n">
@@ -17101,7 +17089,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="B355" t="n">
@@ -17148,7 +17136,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="B356" t="n">
@@ -17195,7 +17183,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="B357" t="n">
@@ -17242,7 +17230,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B358" t="n">
@@ -17289,7 +17277,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="B359" t="n">
@@ -17336,7 +17324,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="B360" t="n">
@@ -17383,7 +17371,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="B361" t="n">
@@ -17430,7 +17418,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="B362" t="n">
@@ -17477,7 +17465,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B363" t="n">
@@ -17524,7 +17512,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="B364" t="n">
@@ -17571,7 +17559,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="B365" t="n">
@@ -17618,7 +17606,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="B366" t="n">
@@ -17665,7 +17653,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="B367" t="n">
@@ -17712,7 +17700,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B368" t="n">
@@ -17759,7 +17747,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="B369" t="n">
@@ -17806,7 +17794,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="B370" t="n">
@@ -17853,7 +17841,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="B371" t="n">
@@ -17900,7 +17888,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B372" t="n">
@@ -17947,7 +17935,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B373" t="n">
@@ -17994,7 +17982,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="B374" t="n">
@@ -18041,7 +18029,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>45356</v>
       </c>
       <c r="B375" t="n">
@@ -18088,7 +18076,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>45357</v>
       </c>
       <c r="B376" t="n">
@@ -18135,7 +18123,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>45358</v>
       </c>
       <c r="B377" t="n">
@@ -18182,7 +18170,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B378" t="n">
@@ -18229,7 +18217,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="B379" t="n">
@@ -18276,7 +18264,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>45363</v>
       </c>
       <c r="B380" t="n">
@@ -18323,7 +18311,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>45364</v>
       </c>
       <c r="B381" t="n">
@@ -18370,7 +18358,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>45365</v>
       </c>
       <c r="B382" t="n">
@@ -18417,7 +18405,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B383" t="n">
@@ -18464,7 +18452,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>45369</v>
       </c>
       <c r="B384" t="n">
@@ -18511,7 +18499,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>45370</v>
       </c>
       <c r="B385" t="n">
@@ -18558,7 +18546,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>45371</v>
       </c>
       <c r="B386" t="n">
@@ -18605,7 +18593,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>45372</v>
       </c>
       <c r="B387" t="n">
@@ -18652,7 +18640,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B388" t="n">
@@ -18699,7 +18687,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>45376</v>
       </c>
       <c r="B389" t="n">
@@ -18746,7 +18734,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>45377</v>
       </c>
       <c r="B390" t="n">
@@ -18793,7 +18781,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>45378</v>
       </c>
       <c r="B391" t="n">
@@ -18840,7 +18828,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>45379</v>
       </c>
       <c r="B392" t="n">
@@ -18887,7 +18875,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B393" t="n">
@@ -18934,7 +18922,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B394" t="n">
@@ -18981,7 +18969,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>45384</v>
       </c>
       <c r="B395" t="n">
@@ -19028,7 +19016,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>45385</v>
       </c>
       <c r="B396" t="n">
@@ -19075,7 +19063,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>45386</v>
       </c>
       <c r="B397" t="n">
@@ -19122,7 +19110,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B398" t="n">
@@ -19169,7 +19157,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>45390</v>
       </c>
       <c r="B399" t="n">
@@ -19216,7 +19204,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>45391</v>
       </c>
       <c r="B400" t="n">
@@ -19263,7 +19251,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>45397</v>
       </c>
       <c r="B401" t="n">
@@ -19310,7 +19298,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>45398</v>
       </c>
       <c r="B402" t="n">
@@ -19357,7 +19345,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>45399</v>
       </c>
       <c r="B403" t="n">
@@ -19404,7 +19392,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>45400</v>
       </c>
       <c r="B404" t="n">
@@ -19451,7 +19439,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B405" t="n">
@@ -19498,7 +19486,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>45404</v>
       </c>
       <c r="B406" t="n">
@@ -19545,7 +19533,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>45406</v>
       </c>
       <c r="B407" t="n">
@@ -19592,7 +19580,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>45407</v>
       </c>
       <c r="B408" t="n">
@@ -19639,7 +19627,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B409" t="n">
@@ -19686,7 +19674,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>45411</v>
       </c>
       <c r="B410" t="n">
@@ -19733,7 +19721,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B411" t="n">
@@ -19780,7 +19768,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>45414</v>
       </c>
       <c r="B412" t="n">
@@ -19827,7 +19815,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B413" t="n">
@@ -19874,7 +19862,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>45418</v>
       </c>
       <c r="B414" t="n">
@@ -19921,7 +19909,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>45419</v>
       </c>
       <c r="B415" t="n">
@@ -19968,7 +19956,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>45420</v>
       </c>
       <c r="B416" t="n">
@@ -20015,7 +20003,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>45421</v>
       </c>
       <c r="B417" t="n">
@@ -20062,7 +20050,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B418" t="n">
@@ -20109,7 +20097,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>45425</v>
       </c>
       <c r="B419" t="n">
@@ -20156,7 +20144,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>45426</v>
       </c>
       <c r="B420" t="n">
@@ -20203,7 +20191,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="B421" t="n">
@@ -20250,7 +20238,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>45428</v>
       </c>
       <c r="B422" t="n">
@@ -20297,7 +20285,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B423" t="n">
@@ -20344,7 +20332,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>45432</v>
       </c>
       <c r="B424" t="n">
@@ -20391,7 +20379,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>45433</v>
       </c>
       <c r="B425" t="n">
@@ -20438,7 +20426,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>45434</v>
       </c>
       <c r="B426" t="n">
@@ -20485,7 +20473,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>45435</v>
       </c>
       <c r="B427" t="n">
@@ -20532,7 +20520,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B428" t="n">
@@ -20579,7 +20567,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>45439</v>
       </c>
       <c r="B429" t="n">
@@ -20626,7 +20614,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>45440</v>
       </c>
       <c r="B430" t="n">
@@ -20673,7 +20661,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>45441</v>
       </c>
       <c r="B431" t="n">
@@ -20720,7 +20708,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>45442</v>
       </c>
       <c r="B432" t="n">
@@ -20767,7 +20755,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B433" t="n">
@@ -20814,7 +20802,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>45446</v>
       </c>
       <c r="B434" t="n">
@@ -20861,7 +20849,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>45447</v>
       </c>
       <c r="B435" t="n">
@@ -20908,7 +20896,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>45448</v>
       </c>
       <c r="B436" t="n">
@@ -20955,7 +20943,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>45449</v>
       </c>
       <c r="B437" t="n">
@@ -21002,7 +20990,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B438" t="n">
@@ -21049,7 +21037,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>45453</v>
       </c>
       <c r="B439" t="n">
@@ -21096,7 +21084,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="B440" t="n">
@@ -21143,7 +21131,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>45455</v>
       </c>
       <c r="B441" t="n">
@@ -21190,7 +21178,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>45456</v>
       </c>
       <c r="B442" t="n">
@@ -21237,7 +21225,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B443" t="n">
@@ -21284,7 +21272,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="B444" t="n">
@@ -21331,7 +21319,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B445" t="n">
@@ -21378,7 +21366,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B446" t="n">
@@ -21425,7 +21413,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="B447" t="n">
@@ -21472,7 +21460,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="B448" t="n">
@@ -21519,7 +21507,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="B449" t="n">
@@ -21566,7 +21554,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B450" t="n">
@@ -21613,7 +21601,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B451" t="n">
@@ -21660,7 +21648,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="B452" t="n">
@@ -21707,7 +21695,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>45476</v>
       </c>
       <c r="B453" t="n">
@@ -21754,7 +21742,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="B454" t="n">
@@ -21801,7 +21789,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B455" t="n">
@@ -21848,7 +21836,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="B456" t="n">
@@ -21895,7 +21883,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="B457" t="n">
@@ -21942,7 +21930,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>45483</v>
       </c>
       <c r="B458" t="n">
@@ -21989,7 +21977,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>45484</v>
       </c>
       <c r="B459" t="n">
@@ -22036,7 +22024,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B460" t="n">
@@ -22083,7 +22071,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45489</v>
       </c>
       <c r="B461" t="n">
@@ -22130,7 +22118,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="B462" t="n">
@@ -22177,7 +22165,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45491</v>
       </c>
       <c r="B463" t="n">
@@ -22224,7 +22212,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B464" t="n">
@@ -22271,7 +22259,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45495</v>
       </c>
       <c r="B465" t="n">
@@ -22318,7 +22306,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45496</v>
       </c>
       <c r="B466" t="n">
@@ -22365,7 +22353,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45497</v>
       </c>
       <c r="B467" t="n">
@@ -22412,7 +22400,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45498</v>
       </c>
       <c r="B468" t="n">
@@ -22459,7 +22447,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B469" t="n">
@@ -22506,7 +22494,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45502</v>
       </c>
       <c r="B470" t="n">
@@ -22553,7 +22541,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45503</v>
       </c>
       <c r="B471" t="n">
@@ -22600,7 +22588,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B472" t="n">
@@ -22647,7 +22635,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B473" t="n">
@@ -22694,7 +22682,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B474" t="n">
@@ -22741,7 +22729,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45509</v>
       </c>
       <c r="B475" t="n">
@@ -22788,7 +22776,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45510</v>
       </c>
       <c r="B476" t="n">
@@ -22835,7 +22823,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45511</v>
       </c>
       <c r="B477" t="n">
@@ -22882,7 +22870,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45512</v>
       </c>
       <c r="B478" t="n">
@@ -22929,7 +22917,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B479" t="n">
@@ -22976,7 +22964,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45516</v>
       </c>
       <c r="B480" t="n">
@@ -23023,7 +23011,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45517</v>
       </c>
       <c r="B481" t="n">
@@ -23070,7 +23058,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45518</v>
       </c>
       <c r="B482" t="n">
@@ -23117,7 +23105,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45519</v>
       </c>
       <c r="B483" t="n">
@@ -23164,7 +23152,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B484" t="n">
@@ -23211,7 +23199,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45523</v>
       </c>
       <c r="B485" t="n">
@@ -23258,7 +23246,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45524</v>
       </c>
       <c r="B486" t="n">
@@ -23305,7 +23293,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45525</v>
       </c>
       <c r="B487" t="n">
@@ -23352,7 +23340,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45526</v>
       </c>
       <c r="B488" t="n">
@@ -23399,7 +23387,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B489" t="n">
@@ -23446,7 +23434,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45530</v>
       </c>
       <c r="B490" t="n">
@@ -23493,7 +23481,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45531</v>
       </c>
       <c r="B491" t="n">
@@ -23540,7 +23528,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45532</v>
       </c>
       <c r="B492" t="n">
@@ -23587,7 +23575,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>45533</v>
       </c>
       <c r="B493" t="n">
@@ -23634,7 +23622,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>45537</v>
       </c>
       <c r="B494" t="n">
@@ -23681,7 +23669,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>45538</v>
       </c>
       <c r="B495" t="n">
@@ -23728,7 +23716,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>45539</v>
       </c>
       <c r="B496" t="n">
@@ -23775,7 +23763,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>45540</v>
       </c>
       <c r="B497" t="n">
@@ -23822,7 +23810,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B498" t="n">
@@ -23869,7 +23857,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>45544</v>
       </c>
       <c r="B499" t="n">
@@ -23916,7 +23904,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>45545</v>
       </c>
       <c r="B500" t="n">
@@ -23963,7 +23951,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>45546</v>
       </c>
       <c r="B501" t="n">
@@ -24010,7 +23998,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>45547</v>
       </c>
       <c r="B502" t="n">
@@ -24057,7 +24045,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B503" t="n">
@@ -24104,7 +24092,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="1" t="n">
         <v>45551</v>
       </c>
       <c r="B504" t="n">
@@ -24151,7 +24139,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="1" t="n">
         <v>45552</v>
       </c>
       <c r="B505" t="n">
@@ -24198,7 +24186,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="1" t="n">
         <v>45553</v>
       </c>
       <c r="B506" t="n">
@@ -24245,7 +24233,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="1" t="n">
         <v>45554</v>
       </c>
       <c r="B507" t="n">
@@ -24292,7 +24280,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B508" t="n">
@@ -24339,7 +24327,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="1" t="n">
         <v>45558</v>
       </c>
       <c r="B509" t="n">
@@ -24386,7 +24374,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="1" t="n">
         <v>45559</v>
       </c>
       <c r="B510" t="n">
@@ -24433,7 +24421,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="1" t="n">
         <v>45560</v>
       </c>
       <c r="B511" t="n">
@@ -24480,7 +24468,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="1" t="n">
         <v>45561</v>
       </c>
       <c r="B512" t="n">
@@ -24527,7 +24515,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B513" t="n">
@@ -24574,7 +24562,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B514" t="n">
@@ -24621,7 +24609,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B515" t="n">
@@ -24668,7 +24656,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="1" t="n">
         <v>45567</v>
       </c>
       <c r="B516" t="n">
@@ -24715,7 +24703,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="1" t="n">
         <v>45568</v>
       </c>
       <c r="B517" t="n">
@@ -24762,7 +24750,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B518" t="n">
@@ -24809,7 +24797,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="1" t="n">
         <v>45572</v>
       </c>
       <c r="B519" t="n">
@@ -24856,7 +24844,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="1" t="n">
         <v>45573</v>
       </c>
       <c r="B520" t="n">
@@ -24903,7 +24891,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="1" t="n">
         <v>45574</v>
       </c>
       <c r="B521" t="n">
@@ -24950,7 +24938,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="1" t="n">
         <v>45575</v>
       </c>
       <c r="B522" t="n">
@@ -24997,7 +24985,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B523" t="n">
@@ -25044,7 +25032,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="1" t="n">
         <v>45579</v>
       </c>
       <c r="B524" t="n">
@@ -25091,7 +25079,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="1" t="n">
         <v>45580</v>
       </c>
       <c r="B525" t="n">
@@ -25138,7 +25126,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="1" t="n">
         <v>45581</v>
       </c>
       <c r="B526" t="n">
@@ -25185,7 +25173,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="1" t="n">
         <v>45582</v>
       </c>
       <c r="B527" t="n">
@@ -25232,7 +25220,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B528" t="n">
@@ -25279,7 +25267,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="1" t="n">
         <v>45586</v>
       </c>
       <c r="B529" t="n">
@@ -25326,7 +25314,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="1" t="n">
         <v>45587</v>
       </c>
       <c r="B530" t="n">
@@ -25373,7 +25361,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="1" t="n">
         <v>45588</v>
       </c>
       <c r="B531" t="n">
@@ -25420,7 +25408,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="1" t="n">
         <v>45589</v>
       </c>
       <c r="B532" t="n">
@@ -25467,7 +25455,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B533" t="n">
@@ -25514,7 +25502,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="1" t="n">
         <v>45593</v>
       </c>
       <c r="B534" t="n">
@@ -25561,7 +25549,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="1" t="n">
         <v>45595</v>
       </c>
       <c r="B535" t="n">
@@ -25608,7 +25596,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B536" t="n">
@@ -25655,7 +25643,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B537" t="n">
@@ -25702,7 +25690,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="1" t="n">
         <v>45600</v>
       </c>
       <c r="B538" t="n">
@@ -25749,7 +25737,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="1" t="n">
         <v>45601</v>
       </c>
       <c r="B539" t="n">
@@ -25796,7 +25784,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="1" t="n">
         <v>45602</v>
       </c>
       <c r="B540" t="n">
@@ -25843,7 +25831,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="1" t="n">
         <v>45603</v>
       </c>
       <c r="B541" t="n">
@@ -25890,7 +25878,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B542" t="n">
@@ -25937,7 +25925,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="1" t="n">
         <v>45607</v>
       </c>
       <c r="B543" t="n">
@@ -25984,7 +25972,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="1" t="n">
         <v>45608</v>
       </c>
       <c r="B544" t="n">
@@ -26031,7 +26019,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="1" t="n">
         <v>45609</v>
       </c>
       <c r="B545" t="n">
@@ -26078,7 +26066,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="1" t="n">
         <v>45610</v>
       </c>
       <c r="B546" t="n">
@@ -26125,7 +26113,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B547" t="n">
@@ -26172,7 +26160,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="1" t="n">
         <v>45614</v>
       </c>
       <c r="B548" t="n">
@@ -26219,7 +26207,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="1" t="n">
         <v>45615</v>
       </c>
       <c r="B549" t="n">
@@ -26266,7 +26254,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="1" t="n">
         <v>45616</v>
       </c>
       <c r="B550" t="n">
@@ -26313,7 +26301,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="1" t="n">
         <v>45617</v>
       </c>
       <c r="B551" t="n">
@@ -26360,7 +26348,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B552" t="n">
@@ -26407,7 +26395,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="1" t="n">
         <v>45621</v>
       </c>
       <c r="B553" t="n">
@@ -26454,7 +26442,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="1" t="n">
         <v>45622</v>
       </c>
       <c r="B554" t="n">
@@ -26501,7 +26489,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="B555" t="n">
@@ -26548,7 +26536,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="1" t="n">
         <v>45624</v>
       </c>
       <c r="B556" t="n">
@@ -26595,7 +26583,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B557" t="n">
@@ -26642,7 +26630,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="1" t="n">
         <v>45628</v>
       </c>
       <c r="B558" t="n">
@@ -26689,7 +26677,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="1" t="n">
         <v>45629</v>
       </c>
       <c r="B559" t="n">
@@ -26736,7 +26724,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="1" t="n">
         <v>45630</v>
       </c>
       <c r="B560" t="n">
@@ -26783,7 +26771,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="1" t="n">
         <v>45631</v>
       </c>
       <c r="B561" t="n">
@@ -26830,7 +26818,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B562" t="n">
@@ -26877,7 +26865,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="1" t="n">
         <v>45635</v>
       </c>
       <c r="B563" t="n">
@@ -26924,7 +26912,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="1" t="n">
         <v>45636</v>
       </c>
       <c r="B564" t="n">
@@ -26971,7 +26959,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="1" t="n">
         <v>45637</v>
       </c>
       <c r="B565" t="n">
@@ -27018,7 +27006,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="1" t="n">
         <v>45638</v>
       </c>
       <c r="B566" t="n">
@@ -27065,7 +27053,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B567" t="n">
@@ -27112,7 +27100,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="1" t="n">
         <v>45642</v>
       </c>
       <c r="B568" t="n">
@@ -27159,7 +27147,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="B569" t="n">
@@ -27206,7 +27194,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="1" t="n">
         <v>45644</v>
       </c>
       <c r="B570" t="n">
@@ -27253,7 +27241,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="1" t="n">
         <v>45645</v>
       </c>
       <c r="B571" t="n">
@@ -27300,7 +27288,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B572" t="n">
@@ -27347,7 +27335,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="B573" t="n">
@@ -27394,7 +27382,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="B574" t="n">
@@ -27441,7 +27429,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="1" t="n">
         <v>45651</v>
       </c>
       <c r="B575" t="n">
@@ -27488,7 +27476,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="1" t="n">
         <v>45652</v>
       </c>
       <c r="B576" t="n">
@@ -27535,7 +27523,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B577" t="n">
@@ -27582,7 +27570,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="1" t="n">
         <v>45656</v>
       </c>
       <c r="B578" t="n">
@@ -27629,7 +27617,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B579" t="n">
@@ -27676,7 +27664,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="1" t="n">
         <v>45659</v>
       </c>
       <c r="B580" t="n">
@@ -27723,7 +27711,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B581" t="n">
@@ -27770,7 +27758,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="1" t="n">
         <v>45663</v>
       </c>
       <c r="B582" t="n">
@@ -27817,7 +27805,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="1" t="n">
         <v>45664</v>
       </c>
       <c r="B583" t="n">
@@ -27864,7 +27852,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="1" t="n">
         <v>45665</v>
       </c>
       <c r="B584" t="n">
@@ -27911,7 +27899,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="1" t="n">
         <v>45666</v>
       </c>
       <c r="B585" t="n">
@@ -27958,7 +27946,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B586" t="n">
@@ -28005,7 +27993,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="1" t="n">
         <v>45670</v>
       </c>
       <c r="B587" t="n">
@@ -28052,7 +28040,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="1" t="n">
         <v>45671</v>
       </c>
       <c r="B588" t="n">
@@ -28099,7 +28087,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="1" t="n">
         <v>45672</v>
       </c>
       <c r="B589" t="n">
@@ -28146,7 +28134,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="B590" t="n">
@@ -28193,7 +28181,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B591" t="n">
@@ -28240,7 +28228,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="1" t="n">
         <v>45677</v>
       </c>
       <c r="B592" t="n">
@@ -28287,7 +28275,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="1" t="n">
         <v>45678</v>
       </c>
       <c r="B593" t="n">
@@ -28334,7 +28322,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="1" t="n">
         <v>45679</v>
       </c>
       <c r="B594" t="n">
@@ -28381,7 +28369,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="1" t="n">
         <v>45680</v>
       </c>
       <c r="B595" t="n">
@@ -28428,7 +28416,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B596" t="n">
@@ -28475,7 +28463,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="1" t="n">
         <v>45684</v>
       </c>
       <c r="B597" t="n">
@@ -28522,7 +28510,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="1" t="n">
         <v>45685</v>
       </c>
       <c r="B598" t="n">
@@ -28569,7 +28557,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="1" t="n">
         <v>45686</v>
       </c>
       <c r="B599" t="n">
@@ -28616,7 +28604,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="1" t="n">
         <v>45687</v>
       </c>
       <c r="B600" t="n">
@@ -28663,7 +28651,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B601" t="n">
@@ -28710,7 +28698,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="1" t="n">
         <v>45691</v>
       </c>
       <c r="B602" t="n">
@@ -28757,7 +28745,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="2" t="n">
+      <c r="A603" s="1" t="n">
         <v>45692</v>
       </c>
       <c r="B603" t="n">
@@ -28804,7 +28792,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="2" t="n">
+      <c r="A604" s="1" t="n">
         <v>45693</v>
       </c>
       <c r="B604" t="n">
@@ -28851,7 +28839,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="2" t="n">
+      <c r="A605" s="1" t="n">
         <v>45694</v>
       </c>
       <c r="B605" t="n">
@@ -28898,7 +28886,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="2" t="n">
+      <c r="A606" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B606" t="n">
@@ -28945,7 +28933,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="2" t="n">
+      <c r="A607" s="1" t="n">
         <v>45698</v>
       </c>
       <c r="B607" t="n">
@@ -28992,7 +28980,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="2" t="n">
+      <c r="A608" s="1" t="n">
         <v>45699</v>
       </c>
       <c r="B608" t="n">
@@ -29039,7 +29027,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="2" t="n">
+      <c r="A609" s="1" t="n">
         <v>45700</v>
       </c>
       <c r="B609" t="n">
@@ -29086,7 +29074,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="2" t="n">
+      <c r="A610" s="1" t="n">
         <v>45701</v>
       </c>
       <c r="B610" t="n">
@@ -29133,7 +29121,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="2" t="n">
+      <c r="A611" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B611" t="n">
@@ -29180,7 +29168,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="2" t="n">
+      <c r="A612" s="1" t="n">
         <v>45705</v>
       </c>
       <c r="B612" t="n">
@@ -29227,7 +29215,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="2" t="n">
+      <c r="A613" s="1" t="n">
         <v>45706</v>
       </c>
       <c r="B613" t="n">
@@ -29274,7 +29262,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="2" t="n">
+      <c r="A614" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="B614" t="n">
@@ -29321,7 +29309,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="2" t="n">
+      <c r="A615" s="1" t="n">
         <v>45708</v>
       </c>
       <c r="B615" t="n">
@@ -29368,7 +29356,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="2" t="n">
+      <c r="A616" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B616" t="n">
@@ -29415,7 +29403,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="2" t="n">
+      <c r="A617" s="1" t="n">
         <v>45712</v>
       </c>
       <c r="B617" t="n">
@@ -29462,7 +29450,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="2" t="n">
+      <c r="A618" s="1" t="n">
         <v>45713</v>
       </c>
       <c r="B618" t="n">
@@ -29509,7 +29497,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="2" t="n">
+      <c r="A619" s="1" t="n">
         <v>45714</v>
       </c>
       <c r="B619" t="n">
@@ -29556,7 +29544,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="2" t="n">
+      <c r="A620" s="1" t="n">
         <v>45715</v>
       </c>
       <c r="B620" t="n">
@@ -29603,7 +29591,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="2" t="n">
+      <c r="A621" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B621" t="n">
@@ -29650,7 +29638,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="2" t="n">
+      <c r="A622" s="1" t="n">
         <v>45719</v>
       </c>
       <c r="B622" t="n">
@@ -29697,7 +29685,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="2" t="n">
+      <c r="A623" s="1" t="n">
         <v>45720</v>
       </c>
       <c r="B623" t="n">
@@ -29744,7 +29732,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="2" t="n">
+      <c r="A624" s="1" t="n">
         <v>45721</v>
       </c>
       <c r="B624" t="n">
@@ -29791,7 +29779,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="2" t="n">
+      <c r="A625" s="1" t="n">
         <v>45722</v>
       </c>
       <c r="B625" t="n">
@@ -29838,7 +29826,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="2" t="n">
+      <c r="A626" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B626" t="n">
@@ -29885,7 +29873,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="2" t="n">
+      <c r="A627" s="1" t="n">
         <v>45726</v>
       </c>
       <c r="B627" t="n">
@@ -29932,7 +29920,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="2" t="n">
+      <c r="A628" s="1" t="n">
         <v>45727</v>
       </c>
       <c r="B628" t="n">
@@ -29979,7 +29967,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="2" t="n">
+      <c r="A629" s="1" t="n">
         <v>45728</v>
       </c>
       <c r="B629" t="n">
@@ -30026,7 +30014,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="2" t="n">
+      <c r="A630" s="1" t="n">
         <v>45729</v>
       </c>
       <c r="B630" t="n">
@@ -30073,7 +30061,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="2" t="n">
+      <c r="A631" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B631" t="n">
@@ -30120,7 +30108,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="2" t="n">
+      <c r="A632" s="1" t="n">
         <v>45733</v>
       </c>
       <c r="B632" t="n">
@@ -30167,7 +30155,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="2" t="n">
+      <c r="A633" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="B633" t="n">
@@ -30214,7 +30202,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="2" t="n">
+      <c r="A634" s="1" t="n">
         <v>45735</v>
       </c>
       <c r="B634" t="n">
@@ -30261,7 +30249,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="2" t="n">
+      <c r="A635" s="1" t="n">
         <v>45736</v>
       </c>
       <c r="B635" t="n">
@@ -30308,7 +30296,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="2" t="n">
+      <c r="A636" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B636" t="n">
@@ -30355,7 +30343,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="2" t="n">
+      <c r="A637" s="1" t="n">
         <v>45740</v>
       </c>
       <c r="B637" t="n">
@@ -30402,7 +30390,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="2" t="n">
+      <c r="A638" s="1" t="n">
         <v>45741</v>
       </c>
       <c r="B638" t="n">
@@ -30449,7 +30437,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="2" t="n">
+      <c r="A639" s="1" t="n">
         <v>45742</v>
       </c>
       <c r="B639" t="n">
@@ -30496,7 +30484,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="2" t="n">
+      <c r="A640" s="1" t="n">
         <v>45743</v>
       </c>
       <c r="B640" t="n">
@@ -30543,7 +30531,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="2" t="n">
+      <c r="A641" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B641" t="n">
@@ -30590,7 +30578,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="2" t="n">
+      <c r="A642" s="1" t="n">
         <v>45749</v>
       </c>
       <c r="B642" t="n">
@@ -30637,7 +30625,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="2" t="n">
+      <c r="A643" s="1" t="n">
         <v>45750</v>
       </c>
       <c r="B643" t="n">
@@ -30684,7 +30672,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="2" t="n">
+      <c r="A644" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B644" t="n">
@@ -30731,7 +30719,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="2" t="n">
+      <c r="A645" s="1" t="n">
         <v>45754</v>
       </c>
       <c r="B645" t="n">
@@ -30778,7 +30766,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="2" t="n">
+      <c r="A646" s="1" t="n">
         <v>45755</v>
       </c>
       <c r="B646" t="n">
@@ -30825,7 +30813,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="2" t="n">
+      <c r="A647" s="1" t="n">
         <v>45756</v>
       </c>
       <c r="B647" t="n">
@@ -30872,7 +30860,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="2" t="n">
+      <c r="A648" s="1" t="n">
         <v>45757</v>
       </c>
       <c r="B648" t="n">
@@ -30919,7 +30907,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="2" t="n">
+      <c r="A649" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B649" t="n">
@@ -30966,7 +30954,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="2" t="n">
+      <c r="A650" s="1" t="n">
         <v>45761</v>
       </c>
       <c r="B650" t="n">
@@ -31013,7 +31001,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="2" t="n">
+      <c r="A651" s="1" t="n">
         <v>45762</v>
       </c>
       <c r="B651" t="n">
@@ -31060,7 +31048,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="2" t="n">
+      <c r="A652" s="1" t="n">
         <v>45763</v>
       </c>
       <c r="B652" t="n">
@@ -31107,7 +31095,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="2" t="n">
+      <c r="A653" s="1" t="n">
         <v>45764</v>
       </c>
       <c r="B653" t="n">
@@ -31154,7 +31142,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="2" t="n">
+      <c r="A654" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B654" t="n">
@@ -31201,7 +31189,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="2" t="n">
+      <c r="A655" s="1" t="n">
         <v>45768</v>
       </c>
       <c r="B655" t="n">
@@ -31248,7 +31236,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="2" t="n">
+      <c r="A656" s="1" t="n">
         <v>45769</v>
       </c>
       <c r="B656" t="n">
@@ -31295,7 +31283,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" s="2" t="n">
+      <c r="A657" s="1" t="n">
         <v>45771</v>
       </c>
       <c r="B657" t="n">
@@ -31342,7 +31330,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" s="2" t="n">
+      <c r="A658" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B658" t="n">
@@ -31389,7 +31377,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="2" t="n">
+      <c r="A659" s="1" t="n">
         <v>45775</v>
       </c>
       <c r="B659" t="n">
@@ -31436,7 +31424,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" s="2" t="n">
+      <c r="A660" s="1" t="n">
         <v>45776</v>
       </c>
       <c r="B660" t="n">
@@ -31483,7 +31471,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" s="2" t="n">
+      <c r="A661" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B661" t="n">
@@ -31530,7 +31518,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="2" t="n">
+      <c r="A662" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B662" t="n">
@@ -31577,7 +31565,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" s="2" t="n">
+      <c r="A663" s="1" t="n">
         <v>45782</v>
       </c>
       <c r="B663" t="n">
@@ -31624,7 +31612,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="2" t="n">
+      <c r="A664" s="1" t="n">
         <v>45783</v>
       </c>
       <c r="B664" t="n">
@@ -31671,7 +31659,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" s="2" t="n">
+      <c r="A665" s="1" t="n">
         <v>45784</v>
       </c>
       <c r="B665" t="n">
@@ -31718,7 +31706,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="2" t="n">
+      <c r="A666" s="1" t="n">
         <v>45785</v>
       </c>
       <c r="B666" t="n">
@@ -31765,7 +31753,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" s="2" t="n">
+      <c r="A667" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B667" t="n">
@@ -31812,7 +31800,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" s="2" t="n">
+      <c r="A668" s="1" t="n">
         <v>45789</v>
       </c>
       <c r="B668" t="n">
@@ -31859,7 +31847,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="2" t="n">
+      <c r="A669" s="1" t="n">
         <v>45790</v>
       </c>
       <c r="B669" t="n">
@@ -31906,7 +31894,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" s="2" t="n">
+      <c r="A670" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="B670" t="n">
@@ -31953,7 +31941,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" s="2" t="n">
+      <c r="A671" s="1" t="n">
         <v>45792</v>
       </c>
       <c r="B671" t="n">
@@ -32000,7 +31988,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" s="2" t="n">
+      <c r="A672" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B672" t="n">
@@ -32047,7 +32035,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="2" t="n">
+      <c r="A673" s="1" t="n">
         <v>45797</v>
       </c>
       <c r="B673" t="n">
@@ -32094,7 +32082,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" s="2" t="n">
+      <c r="A674" s="1" t="n">
         <v>45798</v>
       </c>
       <c r="B674" t="n">
@@ -32141,7 +32129,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" s="2" t="n">
+      <c r="A675" s="1" t="n">
         <v>45799</v>
       </c>
       <c r="B675" t="n">
@@ -32188,7 +32176,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="2" t="n">
+      <c r="A676" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B676" t="n">
@@ -32235,7 +32223,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" s="2" t="n">
+      <c r="A677" s="1" t="n">
         <v>45803</v>
       </c>
       <c r="B677" t="n">
@@ -32282,7 +32270,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" s="2" t="n">
+      <c r="A678" s="1" t="n">
         <v>45804</v>
       </c>
       <c r="B678" t="n">
@@ -32329,7 +32317,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" s="2" t="n">
+      <c r="A679" s="1" t="n">
         <v>45805</v>
       </c>
       <c r="B679" t="n">
@@ -32376,7 +32364,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" s="2" t="n">
+      <c r="A680" s="1" t="n">
         <v>45806</v>
       </c>
       <c r="B680" t="n">
@@ -32423,7 +32411,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="2" t="n">
+      <c r="A681" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B681" t="n">
@@ -32470,7 +32458,7 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" s="2" t="n">
+      <c r="A682" s="1" t="n">
         <v>45810</v>
       </c>
       <c r="B682" t="n">
@@ -32517,7 +32505,7 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" s="2" t="n">
+      <c r="A683" s="1" t="n">
         <v>45811</v>
       </c>
       <c r="B683" t="n">
@@ -32564,7 +32552,7 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" s="2" t="n">
+      <c r="A684" s="1" t="n">
         <v>45812</v>
       </c>
       <c r="B684" t="n">
@@ -32611,7 +32599,7 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" s="2" t="n">
+      <c r="A685" s="1" t="n">
         <v>45813</v>
       </c>
       <c r="B685" t="n">
@@ -32658,7 +32646,7 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" s="2" t="n">
+      <c r="A686" s="1" t="n">
         <v>45818</v>
       </c>
       <c r="B686" t="n">
@@ -32705,7 +32693,7 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" s="2" t="n">
+      <c r="A687" s="1" t="n">
         <v>45819</v>
       </c>
       <c r="B687" t="n">
@@ -32752,7 +32740,7 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="2" t="n">
+      <c r="A688" s="1" t="n">
         <v>45820</v>
       </c>
       <c r="B688" t="n">
@@ -32799,7 +32787,7 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" s="2" t="n">
+      <c r="A689" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B689" t="n">
@@ -32846,7 +32834,7 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" s="2" t="n">
+      <c r="A690" s="1" t="n">
         <v>45824</v>
       </c>
       <c r="B690" t="n">
@@ -32893,7 +32881,7 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" s="2" t="n">
+      <c r="A691" s="1" t="n">
         <v>45825</v>
       </c>
       <c r="B691" t="n">
@@ -32940,7 +32928,7 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" s="2" t="n">
+      <c r="A692" s="1" t="n">
         <v>45826</v>
       </c>
       <c r="B692" t="n">
@@ -32987,7 +32975,7 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" s="2" t="n">
+      <c r="A693" s="1" t="n">
         <v>45827</v>
       </c>
       <c r="B693" t="n">
@@ -33034,7 +33022,7 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" s="2" t="n">
+      <c r="A694" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B694" t="n">
@@ -33081,7 +33069,7 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" s="2" t="n">
+      <c r="A695" s="1" t="n">
         <v>45831</v>
       </c>
       <c r="B695" t="n">
@@ -33128,7 +33116,7 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" s="2" t="n">
+      <c r="A696" s="1" t="n">
         <v>45832</v>
       </c>
       <c r="B696" t="n">
@@ -33175,7 +33163,7 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" s="2" t="n">
+      <c r="A697" s="1" t="n">
         <v>45833</v>
       </c>
       <c r="B697" t="n">
@@ -33222,7 +33210,7 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" s="2" t="n">
+      <c r="A698" s="1" t="n">
         <v>45834</v>
       </c>
       <c r="B698" t="n">
@@ -33269,7 +33257,7 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" s="2" t="n">
+      <c r="A699" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B699" t="n">
@@ -33316,7 +33304,7 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" s="2" t="n">
+      <c r="A700" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B700" t="n">
@@ -33363,7 +33351,7 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" s="2" t="n">
+      <c r="A701" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B701" t="n">
@@ -33410,7 +33398,7 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" s="2" t="n">
+      <c r="A702" s="1" t="n">
         <v>45840</v>
       </c>
       <c r="B702" t="n">
@@ -33457,7 +33445,7 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" s="2" t="n">
+      <c r="A703" s="1" t="n">
         <v>45841</v>
       </c>
       <c r="B703" t="n">
@@ -33504,7 +33492,7 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" s="2" t="n">
+      <c r="A704" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B704" t="n">
@@ -33551,7 +33539,7 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" s="2" t="n">
+      <c r="A705" s="1" t="n">
         <v>45845</v>
       </c>
       <c r="B705" t="n">
@@ -33598,7 +33586,7 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" s="2" t="n">
+      <c r="A706" s="1" t="n">
         <v>45846</v>
       </c>
       <c r="B706" t="n">
@@ -33645,7 +33633,7 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" s="2" t="n">
+      <c r="A707" s="1" t="n">
         <v>45847</v>
       </c>
       <c r="B707" t="n">
@@ -33692,7 +33680,7 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" s="2" t="n">
+      <c r="A708" s="1" t="n">
         <v>45848</v>
       </c>
       <c r="B708" t="n">
@@ -33739,7 +33727,7 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" s="2" t="n">
+      <c r="A709" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B709" t="n">
@@ -33786,7 +33774,7 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" s="2" t="n">
+      <c r="A710" s="1" t="n">
         <v>45852</v>
       </c>
       <c r="B710" t="n">
@@ -33833,7 +33821,7 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" s="2" t="n">
+      <c r="A711" s="1" t="n">
         <v>45854</v>
       </c>
       <c r="B711" t="n">
@@ -33880,7 +33868,7 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" s="2" t="n">
+      <c r="A712" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="B712" t="n">
@@ -33927,7 +33915,7 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" s="2" t="n">
+      <c r="A713" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B713" t="n">
@@ -33974,7 +33962,7 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" s="2" t="n">
+      <c r="A714" s="1" t="n">
         <v>45859</v>
       </c>
       <c r="B714" t="n">
@@ -34021,7 +34009,7 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" s="2" t="n">
+      <c r="A715" s="1" t="n">
         <v>45860</v>
       </c>
       <c r="B715" t="n">
@@ -34068,7 +34056,7 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" s="2" t="n">
+      <c r="A716" s="1" t="n">
         <v>45861</v>
       </c>
       <c r="B716" t="n">
@@ -34115,7 +34103,7 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" s="2" t="n">
+      <c r="A717" s="1" t="n">
         <v>45862</v>
       </c>
       <c r="B717" t="n">
@@ -34162,7 +34150,7 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" s="2" t="n">
+      <c r="A718" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B718" t="n">
@@ -34209,7 +34197,7 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" s="2" t="n">
+      <c r="A719" s="1" t="n">
         <v>45866</v>
       </c>
       <c r="B719" t="n">
@@ -34256,7 +34244,7 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" s="2" t="n">
+      <c r="A720" s="1" t="n">
         <v>45867</v>
       </c>
       <c r="B720" t="n">
@@ -34303,7 +34291,7 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" s="2" t="n">
+      <c r="A721" s="1" t="n">
         <v>45868</v>
       </c>
       <c r="B721" t="n">
@@ -34350,7 +34338,7 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" s="2" t="n">
+      <c r="A722" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B722" t="n">
@@ -34397,7 +34385,7 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" s="2" t="n">
+      <c r="A723" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B723" t="n">
@@ -34444,7 +34432,7 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" s="2" t="n">
+      <c r="A724" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="B724" t="n">
@@ -34491,7 +34479,7 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" s="2" t="n">
+      <c r="A725" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="B725" t="n">
@@ -34538,7 +34526,7 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" s="2" t="n">
+      <c r="A726" s="1" t="n">
         <v>45875</v>
       </c>
       <c r="B726" t="n">
@@ -34585,7 +34573,7 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" s="2" t="n">
+      <c r="A727" s="1" t="n">
         <v>45876</v>
       </c>
       <c r="B727" t="n">
@@ -34632,7 +34620,7 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" s="2" t="n">
+      <c r="A728" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B728" t="n">
@@ -34679,7 +34667,7 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" s="2" t="n">
+      <c r="A729" s="1" t="n">
         <v>45880</v>
       </c>
       <c r="B729" t="n">
@@ -34726,7 +34714,7 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" s="2" t="n">
+      <c r="A730" s="1" t="n">
         <v>45881</v>
       </c>
       <c r="B730" t="n">
@@ -34773,7 +34761,7 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" s="2" t="n">
+      <c r="A731" s="1" t="n">
         <v>45882</v>
       </c>
       <c r="B731" t="n">
@@ -34820,7 +34808,7 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" s="2" t="n">
+      <c r="A732" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="B732" t="n">
@@ -34867,7 +34855,7 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" s="2" t="n">
+      <c r="A733" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B733" t="n">
@@ -34914,7 +34902,7 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" s="2" t="n">
+      <c r="A734" s="1" t="n">
         <v>45887</v>
       </c>
       <c r="B734" t="n">
@@ -34961,7 +34949,7 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" s="2" t="n">
+      <c r="A735" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="B735" t="n">
@@ -35008,7 +34996,7 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" s="2" t="n">
+      <c r="A736" s="1" t="n">
         <v>45889</v>
       </c>
       <c r="B736" t="n">
@@ -35055,7 +35043,7 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" s="2" t="n">
+      <c r="A737" s="1" t="n">
         <v>45890</v>
       </c>
       <c r="B737" t="n">
@@ -35102,7 +35090,7 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" s="2" t="n">
+      <c r="A738" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B738" t="n">
@@ -35149,7 +35137,7 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="2" t="n">
+      <c r="A739" s="1" t="n">
         <v>45894</v>
       </c>
       <c r="B739" t="n">
@@ -35196,7 +35184,7 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" s="2" t="n">
+      <c r="A740" s="1" t="n">
         <v>45895</v>
       </c>
       <c r="B740" t="n">
@@ -35243,7 +35231,7 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" s="2" t="n">
+      <c r="A741" s="1" t="n">
         <v>45896</v>
       </c>
       <c r="B741" t="n">
@@ -35290,7 +35278,7 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" s="2" t="n">
+      <c r="A742" s="1" t="n">
         <v>45897</v>
       </c>
       <c r="B742" t="n">
@@ -35337,7 +35325,7 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" s="2" t="n">
+      <c r="A743" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B743" t="n">
@@ -35384,7 +35372,7 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" s="2" t="n">
+      <c r="A744" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B744" t="n">
@@ -35431,7 +35419,7 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" s="2" t="n">
+      <c r="A745" s="1" t="n">
         <v>45902</v>
       </c>
       <c r="B745" t="n">
@@ -35478,7 +35466,7 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="2" t="n">
+      <c r="A746" s="1" t="n">
         <v>45903</v>
       </c>
       <c r="B746" t="n">
@@ -35525,7 +35513,7 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" s="2" t="n">
+      <c r="A747" s="1" t="n">
         <v>45904</v>
       </c>
       <c r="B747" t="n">
@@ -35572,7 +35560,7 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" s="2" t="n">
+      <c r="A748" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B748" t="n">
@@ -35619,7 +35607,7 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" s="2" t="n">
+      <c r="A749" s="1" t="n">
         <v>45908</v>
       </c>
       <c r="B749" t="n">
@@ -35666,7 +35654,7 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" s="2" t="n">
+      <c r="A750" s="1" t="n">
         <v>45909</v>
       </c>
       <c r="B750" t="n">
@@ -35713,7 +35701,7 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" s="2" t="n">
+      <c r="A751" s="1" t="n">
         <v>45910</v>
       </c>
       <c r="B751" t="n">
@@ -35760,7 +35748,7 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" s="2" t="n">
+      <c r="A752" s="1" t="n">
         <v>45911</v>
       </c>
       <c r="B752" t="n">
@@ -35807,7 +35795,7 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" s="2" t="n">
+      <c r="A753" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B753" t="n">
@@ -35854,7 +35842,7 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" s="2" t="n">
+      <c r="A754" s="1" t="n">
         <v>45915</v>
       </c>
       <c r="B754" t="n">
@@ -35901,7 +35889,7 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" s="2" t="n">
+      <c r="A755" s="1" t="n">
         <v>45916</v>
       </c>
       <c r="B755" t="n">
@@ -35948,7 +35936,7 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" s="2" t="n">
+      <c r="A756" s="1" t="n">
         <v>45917</v>
       </c>
       <c r="B756" t="n">
@@ -35995,7 +35983,7 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" s="2" t="n">
+      <c r="A757" s="1" t="n">
         <v>45918</v>
       </c>
       <c r="B757" t="n">
@@ -36042,7 +36030,7 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" s="2" t="n">
+      <c r="A758" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B758" t="n">
@@ -36089,7 +36077,7 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" s="2" t="n">
+      <c r="A759" s="1" t="n">
         <v>45922</v>
       </c>
       <c r="B759" t="n">
@@ -36136,7 +36124,7 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" s="2" t="n">
+      <c r="A760" s="1" t="n">
         <v>45923</v>
       </c>
       <c r="B760" t="n">
@@ -36183,7 +36171,7 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" s="2" t="n">
+      <c r="A761" s="1" t="n">
         <v>45924</v>
       </c>
       <c r="B761" t="n">
@@ -36230,7 +36218,7 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="2" t="n">
+      <c r="A762" s="1" t="n">
         <v>45925</v>
       </c>
       <c r="B762" t="n">
@@ -36277,7 +36265,7 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" s="2" t="n">
+      <c r="A763" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B763" t="n">
@@ -36324,7 +36312,7 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" s="2" t="n">
+      <c r="A764" s="1" t="n">
         <v>45929</v>
       </c>
       <c r="B764" t="n">
@@ -36371,7 +36359,7 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" s="2" t="n">
+      <c r="A765" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B765" t="n">
@@ -36418,7 +36406,7 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" s="2" t="n">
+      <c r="A766" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B766" t="n">
@@ -36465,7 +36453,7 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" s="2" t="n">
+      <c r="A767" s="1" t="n">
         <v>45932</v>
       </c>
       <c r="B767" t="n">
@@ -36512,7 +36500,7 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" s="2" t="n">
+      <c r="A768" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B768" t="n">
@@ -36559,7 +36547,7 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" s="2" t="n">
+      <c r="A769" s="1" t="n">
         <v>45936</v>
       </c>
       <c r="B769" t="n">
@@ -36606,7 +36594,7 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" s="2" t="n">
+      <c r="A770" s="1" t="n">
         <v>45937</v>
       </c>
       <c r="B770" t="n">
@@ -36653,7 +36641,7 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" s="2" t="n">
+      <c r="A771" s="1" t="n">
         <v>45938</v>
       </c>
       <c r="B771" t="n">
@@ -36700,7 +36688,7 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" s="2" t="n">
+      <c r="A772" s="1" t="n">
         <v>45939</v>
       </c>
       <c r="B772" t="n">
@@ -36747,7 +36735,7 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" s="2" t="n">
+      <c r="A773" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B773" t="n">
@@ -36794,7 +36782,7 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" s="2" t="n">
+      <c r="A774" s="1" t="n">
         <v>45943</v>
       </c>
       <c r="B774" t="n">
@@ -36841,7 +36829,7 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" s="2" t="n">
+      <c r="A775" s="1" t="n">
         <v>45944</v>
       </c>
       <c r="B775" t="n">
@@ -36888,7 +36876,7 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" s="2" t="n">
+      <c r="A776" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="B776" t="n">
@@ -36935,7 +36923,7 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" s="2" t="n">
+      <c r="A777" s="1" t="n">
         <v>45946</v>
       </c>
       <c r="B777" t="n">
@@ -36982,7 +36970,7 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" s="2" t="n">
+      <c r="A778" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B778" t="n">
@@ -37029,7 +37017,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="2" t="n">
+      <c r="A779" s="1" t="n">
         <v>45950</v>
       </c>
       <c r="B779" t="n">
@@ -37076,7 +37064,7 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" s="2" t="n">
+      <c r="A780" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="B780" t="n">
@@ -37123,7 +37111,7 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" s="2" t="n">
+      <c r="A781" s="1" t="n">
         <v>45952</v>
       </c>
       <c r="B781" t="n">
@@ -37170,7 +37158,7 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="2" t="n">
+      <c r="A782" s="1" t="n">
         <v>45953</v>
       </c>
       <c r="B782" t="n">
@@ -37217,7 +37205,7 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" s="2" t="n">
+      <c r="A783" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B783" t="n">
@@ -37264,7 +37252,7 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" s="2" t="n">
+      <c r="A784" s="1" t="n">
         <v>45957</v>
       </c>
       <c r="B784" t="n">
@@ -37311,7 +37299,7 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" s="2" t="n">
+      <c r="A785" s="1" t="n">
         <v>45958</v>
       </c>
       <c r="B785" t="n">
@@ -37358,7 +37346,7 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" s="2" t="n">
+      <c r="A786" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="B786" t="n">
@@ -37405,7 +37393,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" s="2" t="n">
+      <c r="A787" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B787" t="n">
@@ -37452,7 +37440,7 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" s="2" t="n">
+      <c r="A788" s="1" t="n">
         <v>45964</v>
       </c>
       <c r="B788" t="n">
@@ -37499,7 +37487,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" s="2" t="n">
+      <c r="A789" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B789" t="n">
@@ -37546,7 +37534,7 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" s="2" t="n">
+      <c r="A790" s="1" t="n">
         <v>45966</v>
       </c>
       <c r="B790" t="n">
@@ -37593,7 +37581,7 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="2" t="n">
+      <c r="A791" s="1" t="n">
         <v>45967</v>
       </c>
       <c r="B791" t="n">
@@ -37640,7 +37628,7 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" s="2" t="n">
+      <c r="A792" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B792" t="n">
@@ -37687,7 +37675,7 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" s="2" t="n">
+      <c r="A793" s="1" t="n">
         <v>45971</v>
       </c>
       <c r="B793" t="n">
@@ -37734,7 +37722,7 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" s="2" t="n">
+      <c r="A794" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="B794" t="n">
@@ -37781,7 +37769,7 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" s="2" t="n">
+      <c r="A795" s="1" t="n">
         <v>45973</v>
       </c>
       <c r="B795" t="n">
@@ -37828,7 +37816,7 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" s="2" t="n">
+      <c r="A796" s="1" t="n">
         <v>45974</v>
       </c>
       <c r="B796" t="n">
@@ -37875,7 +37863,7 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" s="2" t="n">
+      <c r="A797" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B797" t="n">
@@ -37922,7 +37910,7 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" s="2" t="n">
+      <c r="A798" s="1" t="n">
         <v>45978</v>
       </c>
       <c r="B798" t="n">
@@ -37969,7 +37957,7 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" s="2" t="n">
+      <c r="A799" s="1" t="n">
         <v>45979</v>
       </c>
       <c r="B799" t="n">
@@ -38016,7 +38004,7 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" s="2" t="n">
+      <c r="A800" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="B800" t="n">
@@ -38063,7 +38051,7 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" s="2" t="n">
+      <c r="A801" s="1" t="n">
         <v>45981</v>
       </c>
       <c r="B801" t="n">
@@ -38110,7 +38098,7 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" s="2" t="n">
+      <c r="A802" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B802" t="n">
@@ -38157,7 +38145,7 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" s="2" t="n">
+      <c r="A803" s="1" t="n">
         <v>45985</v>
       </c>
       <c r="B803" t="n">
@@ -38204,7 +38192,7 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" s="2" t="n">
+      <c r="A804" s="1" t="n">
         <v>45986</v>
       </c>
       <c r="B804" t="n">
@@ -38251,7 +38239,7 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="2" t="n">
+      <c r="A805" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="B805" t="n">
@@ -38298,7 +38286,7 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" s="2" t="n">
+      <c r="A806" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="B806" t="n">
@@ -38345,7 +38333,7 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" s="2" t="n">
+      <c r="A807" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B807" t="n">
@@ -38392,7 +38380,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" s="2" t="n">
+      <c r="A808" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B808" t="n">
@@ -38439,7 +38427,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" s="2" t="n">
+      <c r="A809" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="B809" t="n">
@@ -38486,7 +38474,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" s="2" t="n">
+      <c r="A810" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="B810" t="n">
@@ -38533,7 +38521,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" s="2" t="n">
+      <c r="A811" s="1" t="n">
         <v>45995</v>
       </c>
       <c r="B811" t="n">
@@ -38580,7 +38568,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" s="2" t="n">
+      <c r="A812" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B812" t="n">
@@ -38627,7 +38615,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" s="2" t="n">
+      <c r="A813" s="1" t="n">
         <v>45999</v>
       </c>
       <c r="B813" t="n">
@@ -38674,7 +38662,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" s="2" t="n">
+      <c r="A814" s="1" t="n">
         <v>46000</v>
       </c>
       <c r="B814" t="n">
@@ -38721,7 +38709,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" s="2" t="n">
+      <c r="A815" s="1" t="n">
         <v>46001</v>
       </c>
       <c r="B815" t="n">
@@ -38768,7 +38756,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" s="2" t="n">
+      <c r="A816" s="1" t="n">
         <v>46002</v>
       </c>
       <c r="B816" t="n">
@@ -38815,7 +38803,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" s="2" t="n">
+      <c r="A817" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B817" t="n">
@@ -38862,7 +38850,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" s="2" t="n">
+      <c r="A818" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="B818" t="n">
@@ -38909,7 +38897,7 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="2" t="n">
+      <c r="A819" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="B819" t="n">
@@ -38956,7 +38944,7 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" s="2" t="n">
+      <c r="A820" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="B820" t="n">
@@ -39003,7 +38991,7 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" s="2" t="n">
+      <c r="A821" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="B821" t="n">
@@ -39050,7 +39038,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" s="2" t="n">
+      <c r="A822" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B822" t="n">
@@ -39097,7 +39085,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" s="2" t="n">
+      <c r="A823" s="1" t="n">
         <v>46013</v>
       </c>
       <c r="B823" t="n">
@@ -39144,7 +39132,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" s="2" t="n">
+      <c r="A824" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="B824" t="n">
@@ -39191,7 +39179,7 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" s="2" t="n">
+      <c r="A825" s="1" t="n">
         <v>46015</v>
       </c>
       <c r="B825" t="n">
@@ -39238,7 +39226,7 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" s="2" t="n">
+      <c r="A826" s="1" t="n">
         <v>46016</v>
       </c>
       <c r="B826" t="n">
@@ -39285,7 +39273,7 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" s="2" t="n">
+      <c r="A827" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B827" t="n">
@@ -39332,7 +39320,7 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="2" t="n">
+      <c r="A828" s="1" t="n">
         <v>46020</v>
       </c>
       <c r="B828" t="n">
@@ -39379,7 +39367,7 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" s="2" t="n">
+      <c r="A829" s="1" t="n">
         <v>46021</v>
       </c>
       <c r="B829" t="n">
@@ -39426,7 +39414,7 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" s="2" t="n">
+      <c r="A830" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B830" t="n">
@@ -39473,7 +39461,7 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" s="2" t="n">
+      <c r="A831" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B831" t="n">
@@ -39520,7 +39508,7 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" s="2" t="n">
+      <c r="A832" s="1" t="n">
         <v>46027</v>
       </c>
       <c r="B832" t="n">
@@ -39567,7 +39555,7 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" s="2" t="n">
+      <c r="A833" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="B833" t="n">
@@ -39614,7 +39602,7 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" s="2" t="n">
+      <c r="A834" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="B834" t="n">
@@ -39661,7 +39649,7 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" s="2" t="n">
+      <c r="A835" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="B835" t="n">
@@ -39708,7 +39696,7 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" s="2" t="n">
+      <c r="A836" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B836" t="n">
@@ -39755,7 +39743,7 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" s="2" t="n">
+      <c r="A837" s="1" t="n">
         <v>46034</v>
       </c>
       <c r="B837" t="n">
@@ -39802,7 +39790,7 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" s="2" t="n">
+      <c r="A838" s="1" t="n">
         <v>46035</v>
       </c>
       <c r="B838" t="n">
@@ -39849,7 +39837,7 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" s="2" t="n">
+      <c r="A839" s="1" t="n">
         <v>46036</v>
       </c>
       <c r="B839" t="n">
@@ -39896,7 +39884,7 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" s="2" t="n">
+      <c r="A840" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="B840" t="n">
@@ -39943,7 +39931,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" s="2" t="n">
+      <c r="A841" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B841" t="n">
@@ -39990,7 +39978,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" s="2" t="n">
+      <c r="A842" s="1" t="n">
         <v>46041</v>
       </c>
       <c r="B842" t="n">
@@ -40037,7 +40025,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" s="2" t="n">
+      <c r="A843" s="1" t="n">
         <v>46042</v>
       </c>
       <c r="B843" t="n">
@@ -40084,7 +40072,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" s="2" t="n">
+      <c r="A844" s="1" t="n">
         <v>46043</v>
       </c>
       <c r="B844" t="n">
@@ -40131,7 +40119,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" s="2" t="n">
+      <c r="A845" s="1" t="n">
         <v>46044</v>
       </c>
       <c r="B845" t="n">
@@ -40178,7 +40166,7 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" s="2" t="n">
+      <c r="A846" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B846" t="n">
@@ -40225,7 +40213,7 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" s="2" t="n">
+      <c r="A847" s="1" t="n">
         <v>46048</v>
       </c>
       <c r="B847" t="n">
@@ -40272,7 +40260,7 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" s="2" t="n">
+      <c r="A848" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="B848" t="n">
@@ -40319,7 +40307,7 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" s="2" t="n">
+      <c r="A849" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="B849" t="n">
@@ -40366,7 +40354,7 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" s="2" t="n">
+      <c r="A850" s="1" t="n">
         <v>46051</v>
       </c>
       <c r="B850" t="n">
@@ -40413,7 +40401,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" s="2" t="n">
+      <c r="A851" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B851" t="n">
@@ -40460,7 +40448,7 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" s="2" t="n">
+      <c r="A852" s="1" t="n">
         <v>46055</v>
       </c>
       <c r="B852" t="n">
@@ -40507,7 +40495,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" s="2" t="n">
+      <c r="A853" s="1" t="n">
         <v>46056</v>
       </c>
       <c r="B853" t="n">
@@ -40554,7 +40542,7 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" s="2" t="n">
+      <c r="A854" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="B854" t="n">
@@ -40601,7 +40589,7 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" s="2" t="n">
+      <c r="A855" s="1" t="n">
         <v>46058</v>
       </c>
       <c r="B855" t="n">
@@ -40648,7 +40636,7 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" s="2" t="n">
+      <c r="A856" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B856" t="n">
@@ -40695,7 +40683,7 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" s="2" t="n">
+      <c r="A857" s="1" t="n">
         <v>46062</v>
       </c>
       <c r="B857" t="n">
@@ -40742,7 +40730,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" s="2" t="n">
+      <c r="A858" s="1" t="n">
         <v>46063</v>
       </c>
       <c r="B858" t="n">
@@ -40789,7 +40777,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" s="2" t="n">
+      <c r="A859" s="1" t="n">
         <v>46064</v>
       </c>
       <c r="B859" t="n">
@@ -40836,7 +40824,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" s="2" t="n">
+      <c r="A860" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="B860" t="n">
@@ -40883,7 +40871,7 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" s="2" t="n">
+      <c r="A861" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B861" t="n">
@@ -40930,7 +40918,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" s="2" t="n">
+      <c r="A862" s="1" t="n">
         <v>46069</v>
       </c>
       <c r="B862" t="n">
@@ -40977,7 +40965,7 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" s="2" t="n">
+      <c r="A863" s="1" t="n">
         <v>46070</v>
       </c>
       <c r="B863" t="n">
@@ -41024,7 +41012,7 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" s="2" t="n">
+      <c r="A864" s="1" t="n">
         <v>46071</v>
       </c>
       <c r="B864" t="n">
@@ -41071,7 +41059,7 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" s="2" t="n">
+      <c r="A865" s="1" t="n">
         <v>46072</v>
       </c>
       <c r="B865" t="n">
@@ -41118,7 +41106,7 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" s="2" t="n">
+      <c r="A866" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B866" t="n">
@@ -41165,7 +41153,7 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" s="2" t="n">
+      <c r="A867" s="1" t="n">
         <v>46076</v>
       </c>
       <c r="B867" t="n">
@@ -41212,7 +41200,7 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" s="2" t="n">
+      <c r="A868" s="1" t="n">
         <v>46077</v>
       </c>
       <c r="B868" t="n">
@@ -41259,7 +41247,7 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" s="2" t="n">
+      <c r="A869" s="1" t="n">
         <v>46078</v>
       </c>
       <c r="B869" t="n">
@@ -41306,7 +41294,7 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" s="2" t="n">
+      <c r="A870" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="B870" t="n">
@@ -41353,7 +41341,7 @@
       </c>
     </row>
     <row r="871">
-      <c r="A871" s="2" t="n">
+      <c r="A871" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B871" t="n">
@@ -41400,7 +41388,7 @@
       </c>
     </row>
     <row r="872">
-      <c r="A872" s="2" t="n">
+      <c r="A872" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="B872" t="n">
@@ -41447,7 +41435,7 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" s="2" t="n">
+      <c r="A873" s="1" t="n">
         <v>46084</v>
       </c>
       <c r="B873" t="n">
@@ -41494,7 +41482,7 @@
       </c>
     </row>
     <row r="874">
-      <c r="A874" s="2" t="n">
+      <c r="A874" s="1" t="n">
         <v>46085</v>
       </c>
       <c r="B874" t="n">
@@ -41541,7 +41529,7 @@
       </c>
     </row>
     <row r="875">
-      <c r="A875" s="2" t="n">
+      <c r="A875" s="1" t="n">
         <v>46086</v>
       </c>
       <c r="B875" t="n">
@@ -41588,7 +41576,7 @@
       </c>
     </row>
     <row r="876">
-      <c r="A876" s="2" t="n">
+      <c r="A876" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B876" t="n">
@@ -41635,7 +41623,7 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" s="2" t="n">
+      <c r="A877" s="1" t="n">
         <v>46090</v>
       </c>
       <c r="B877" t="n">
@@ -41682,7 +41670,7 @@
       </c>
     </row>
     <row r="878">
-      <c r="A878" s="2" t="n">
+      <c r="A878" s="1" t="n">
         <v>46091</v>
       </c>
       <c r="B878" t="n">
@@ -41729,7 +41717,7 @@
       </c>
     </row>
     <row r="879">
-      <c r="A879" s="2" t="n">
+      <c r="A879" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="B879" t="n">
@@ -41776,7 +41764,7 @@
       </c>
     </row>
     <row r="880">
-      <c r="A880" s="2" t="n">
+      <c r="A880" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B880" t="n">
@@ -41823,7 +41811,7 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" s="2" t="n">
+      <c r="A881" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B881" t="n">
@@ -41870,7 +41858,7 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" s="2" t="n">
+      <c r="A882" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B882" t="n">
@@ -41917,7 +41905,7 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" s="2" t="n">
+      <c r="A883" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B883" t="n">
@@ -41964,7 +41952,7 @@
       </c>
     </row>
     <row r="884">
-      <c r="A884" s="2" t="n">
+      <c r="A884" s="1" t="n">
         <v>46099</v>
       </c>
       <c r="B884" t="n">
@@ -42011,7 +41999,7 @@
       </c>
     </row>
     <row r="885">
-      <c r="A885" s="2" t="n">
+      <c r="A885" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="B885" t="n">
@@ -42058,7 +42046,7 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" s="2" t="n">
+      <c r="A886" s="1" t="n">
         <v>46104</v>
       </c>
       <c r="B886" t="n">
@@ -42105,7 +42093,7 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="2" t="n">
+      <c r="A887" s="1" t="n">
         <v>46105</v>
       </c>
       <c r="B887" t="n">
@@ -42152,7 +42140,7 @@
       </c>
     </row>
     <row r="888">
-      <c r="A888" s="2" t="n">
+      <c r="A888" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="B888" t="n">
@@ -42199,7 +42187,7 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" s="2" t="n">
+      <c r="A889" s="1" t="n">
         <v>46107</v>
       </c>
       <c r="B889" t="n">
@@ -42246,7 +42234,7 @@
       </c>
     </row>
     <row r="890">
-      <c r="A890" s="2" t="n">
+      <c r="A890" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B890" t="n">
@@ -42293,7 +42281,7 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" s="2" t="n">
+      <c r="A891" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="B891" t="n">
@@ -42340,7 +42328,7 @@
       </c>
     </row>
     <row r="892">
-      <c r="A892" s="2" t="n">
+      <c r="A892" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B892" t="n">
@@ -42387,7 +42375,7 @@
       </c>
     </row>
     <row r="893">
-      <c r="A893" s="2" t="n">
+      <c r="A893" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B893" t="n">
@@ -42434,7 +42422,7 @@
       </c>
     </row>
     <row r="894">
-      <c r="A894" s="2" t="n">
+      <c r="A894" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="B894" t="n">
@@ -42481,7 +42469,7 @@
       </c>
     </row>
     <row r="895">
-      <c r="A895" s="2" t="n">
+      <c r="A895" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B895" t="n">
@@ -42528,7 +42516,7 @@
       </c>
     </row>
     <row r="896">
-      <c r="A896" s="2" t="n">
+      <c r="A896" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="B896" t="n">
@@ -42575,7 +42563,7 @@
       </c>
     </row>
     <row r="897">
-      <c r="A897" s="2" t="n">
+      <c r="A897" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="B897" t="n">
@@ -42622,7 +42610,7 @@
       </c>
     </row>
     <row r="898">
-      <c r="A898" s="2" t="n">
+      <c r="A898" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="B898" t="n">
@@ -42669,7 +42657,7 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" s="2" t="n">
+      <c r="A899" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="B899" t="n">
@@ -42716,7 +42704,7 @@
       </c>
     </row>
     <row r="900">
-      <c r="A900" s="2" t="n">
+      <c r="A900" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B900" t="n">
@@ -42763,7 +42751,7 @@
       </c>
     </row>
     <row r="901">
-      <c r="A901" s="2" t="n">
+      <c r="A901" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="B901" t="n">
@@ -42810,7 +42798,7 @@
       </c>
     </row>
     <row r="902">
-      <c r="A902" s="2" t="n">
+      <c r="A902" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="B902" t="n">
@@ -42857,7 +42845,7 @@
       </c>
     </row>
     <row r="903">
-      <c r="A903" s="2" t="n">
+      <c r="A903" s="1" t="n">
         <v>46127</v>
       </c>
       <c r="B903" t="n">
@@ -42904,7 +42892,7 @@
       </c>
     </row>
     <row r="904">
-      <c r="A904" s="2" t="n">
+      <c r="A904" s="1" t="n">
         <v>46128</v>
       </c>
       <c r="B904" t="n">
@@ -42951,7 +42939,7 @@
       </c>
     </row>
     <row r="905">
-      <c r="A905" s="2" t="n">
+      <c r="A905" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B905" t="n">
@@ -42998,7 +42986,7 @@
       </c>
     </row>
     <row r="906">
-      <c r="A906" s="2" t="n">
+      <c r="A906" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="B906" t="n">
@@ -43045,7 +43033,7 @@
       </c>
     </row>
     <row r="907">
-      <c r="A907" s="2" t="n">
+      <c r="A907" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="B907" t="n">
@@ -43092,7 +43080,7 @@
       </c>
     </row>
     <row r="908">
-      <c r="A908" s="2" t="n">
+      <c r="A908" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="B908" t="n">
@@ -43139,7 +43127,7 @@
       </c>
     </row>
     <row r="909">
-      <c r="A909" s="2" t="n">
+      <c r="A909" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B909" t="n">
@@ -43186,7 +43174,7 @@
       </c>
     </row>
     <row r="910">
-      <c r="A910" s="2" t="n">
+      <c r="A910" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="B910" t="n">
@@ -43233,7 +43221,7 @@
       </c>
     </row>
     <row r="911">
-      <c r="A911" s="2" t="n">
+      <c r="A911" s="1" t="n">
         <v>46140</v>
       </c>
       <c r="B911" t="n">
@@ -43280,7 +43268,7 @@
       </c>
     </row>
     <row r="912">
-      <c r="A912" s="2" t="n">
+      <c r="A912" s="1" t="n">
         <v>46141</v>
       </c>
       <c r="B912" t="n">
@@ -43327,7 +43315,7 @@
       </c>
     </row>
     <row r="913">
-      <c r="A913" s="2" t="n">
+      <c r="A913" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B913" t="n">
@@ -43374,7 +43362,7 @@
       </c>
     </row>
     <row r="914">
-      <c r="A914" s="2" t="n">
+      <c r="A914" s="1" t="n">
         <v>46146</v>
       </c>
       <c r="B914" t="n">
@@ -43421,7 +43409,7 @@
       </c>
     </row>
     <row r="915">
-      <c r="A915" s="2" t="n">
+      <c r="A915" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="B915" t="n">
@@ -43468,7 +43456,7 @@
       </c>
     </row>
     <row r="916">
-      <c r="A916" s="2" t="n">
+      <c r="A916" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="B916" t="n">
@@ -43515,7 +43503,7 @@
       </c>
     </row>
     <row r="917">
-      <c r="A917" s="2" t="n">
+      <c r="A917" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="B917" t="n">
@@ -43562,7 +43550,7 @@
       </c>
     </row>
     <row r="918">
-      <c r="A918" s="2" t="n">
+      <c r="A918" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B918" t="n">
@@ -43609,7 +43597,7 @@
       </c>
     </row>
     <row r="919">
-      <c r="A919" s="2" t="n">
+      <c r="A919" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="B919" t="n">
@@ -43656,7 +43644,7 @@
       </c>
     </row>
     <row r="920">
-      <c r="A920" s="2" t="n">
+      <c r="A920" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="B920" t="n">
@@ -43703,7 +43691,7 @@
       </c>
     </row>
     <row r="921">
-      <c r="A921" s="2" t="n">
+      <c r="A921" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="B921" t="n">
@@ -43750,7 +43738,7 @@
       </c>
     </row>
     <row r="922">
-      <c r="A922" s="2" t="n">
+      <c r="A922" s="1" t="n">
         <v>46156</v>
       </c>
       <c r="B922" t="n">
@@ -43797,7 +43785,7 @@
       </c>
     </row>
     <row r="923">
-      <c r="A923" s="2" t="n">
+      <c r="A923" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B923" t="n">
@@ -43844,7 +43832,7 @@
       </c>
     </row>
     <row r="924">
-      <c r="A924" s="2" t="n">
+      <c r="A924" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B924" t="n">
@@ -43891,7 +43879,7 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" s="2" t="n">
+      <c r="A925" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="B925" t="n">
@@ -43938,7 +43926,7 @@
       </c>
     </row>
     <row r="926">
-      <c r="A926" s="2" t="n">
+      <c r="A926" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B926" t="n">
@@ -43985,7 +43973,7 @@
       </c>
     </row>
     <row r="927">
-      <c r="A927" s="2" t="n">
+      <c r="A927" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B927" t="n">
@@ -44032,7 +44020,7 @@
       </c>
     </row>
     <row r="928">
-      <c r="A928" s="2" t="n">
+      <c r="A928" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="B928" t="n">
@@ -44079,7 +44067,7 @@
       </c>
     </row>
     <row r="929">
-      <c r="A929" s="2" t="n">
+      <c r="A929" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="B929" t="n">
@@ -44126,7 +44114,7 @@
       </c>
     </row>
     <row r="930">
-      <c r="A930" s="2" t="n">
+      <c r="A930" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B930" t="n">
@@ -44173,7 +44161,7 @@
       </c>
     </row>
     <row r="931">
-      <c r="A931" s="2" t="n">
+      <c r="A931" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="B931" t="n">
@@ -44220,7 +44208,7 @@
       </c>
     </row>
     <row r="932">
-      <c r="A932" s="2" t="n">
+      <c r="A932" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="B932" t="n">
@@ -44267,7 +44255,7 @@
       </c>
     </row>
     <row r="933">
-      <c r="A933" s="2" t="n">
+      <c r="A933" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="B933" t="n">
@@ -44314,7 +44302,7 @@
       </c>
     </row>
     <row r="934">
-      <c r="A934" s="2" t="n">
+      <c r="A934" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B934" t="n">
@@ -44361,7 +44349,7 @@
       </c>
     </row>
     <row r="935">
-      <c r="A935" s="2" t="n">
+      <c r="A935" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="B935" t="n">
@@ -44408,7 +44396,7 @@
       </c>
     </row>
     <row r="936">
-      <c r="A936" s="2" t="n">
+      <c r="A936" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="B936" t="n">
@@ -44455,7 +44443,7 @@
       </c>
     </row>
     <row r="937">
-      <c r="A937" s="2" t="n">
+      <c r="A937" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="B937" t="n">
@@ -44502,7 +44490,7 @@
       </c>
     </row>
     <row r="938">
-      <c r="A938" s="2" t="n">
+      <c r="A938" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="B938" t="n">
@@ -44549,7 +44537,7 @@
       </c>
     </row>
     <row r="939">
-      <c r="A939" s="2" t="n">
+      <c r="A939" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B939" t="n">
@@ -44596,7 +44584,7 @@
       </c>
     </row>
     <row r="940">
-      <c r="A940" s="2" t="n">
+      <c r="A940" s="1" t="n">
         <v>46188</v>
       </c>
       <c r="B940" t="n">
@@ -44643,7 +44631,7 @@
       </c>
     </row>
     <row r="941">
-      <c r="A941" s="2" t="n">
+      <c r="A941" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="B941" t="n">
@@ -44690,7 +44678,7 @@
       </c>
     </row>
     <row r="942">
-      <c r="A942" s="2" t="n">
+      <c r="A942" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="B942" t="n">
@@ -44737,7 +44725,7 @@
       </c>
     </row>
     <row r="943">
-      <c r="A943" s="2" t="n">
+      <c r="A943" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="B943" t="n">
@@ -44784,7 +44772,7 @@
       </c>
     </row>
     <row r="944">
-      <c r="A944" s="2" t="n">
+      <c r="A944" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B944" t="n">
@@ -44831,7 +44819,7 @@
       </c>
     </row>
     <row r="945">
-      <c r="A945" s="2" t="n">
+      <c r="A945" s="1" t="n">
         <v>46195</v>
       </c>
       <c r="B945" t="n">
@@ -44878,7 +44866,7 @@
       </c>
     </row>
     <row r="946">
-      <c r="A946" s="2" t="n">
+      <c r="A946" s="1" t="n">
         <v>46196</v>
       </c>
       <c r="B946" t="n">
@@ -44925,7 +44913,7 @@
       </c>
     </row>
     <row r="947">
-      <c r="A947" s="2" t="n">
+      <c r="A947" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="B947" t="n">
@@ -44972,7 +44960,7 @@
       </c>
     </row>
     <row r="948">
-      <c r="A948" s="2" t="n">
+      <c r="A948" s="1" t="n">
         <v>46198</v>
       </c>
       <c r="B948" t="n">
@@ -45019,7 +45007,7 @@
       </c>
     </row>
     <row r="949">
-      <c r="A949" s="2" t="n">
+      <c r="A949" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B949" t="n">
@@ -45066,7 +45054,7 @@
       </c>
     </row>
     <row r="950">
-      <c r="A950" s="2" t="n">
+      <c r="A950" s="1" t="n">
         <v>46202</v>
       </c>
       <c r="B950" t="n">
@@ -45113,7 +45101,7 @@
       </c>
     </row>
     <row r="951">
-      <c r="A951" s="2" t="n">
+      <c r="A951" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B951" t="n">
@@ -45160,7 +45148,7 @@
       </c>
     </row>
     <row r="952">
-      <c r="A952" s="2" t="n">
+      <c r="A952" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B952" t="n">
@@ -45207,7 +45195,7 @@
       </c>
     </row>
     <row r="953">
-      <c r="A953" s="2" t="n">
+      <c r="A953" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="B953" t="n">
@@ -45254,7 +45242,7 @@
       </c>
     </row>
     <row r="954">
-      <c r="A954" s="2" t="n">
+      <c r="A954" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B954" t="n">
@@ -45301,7 +45289,7 @@
       </c>
     </row>
     <row r="955">
-      <c r="A955" s="2" t="n">
+      <c r="A955" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="B955" t="n">
@@ -45348,7 +45336,7 @@
       </c>
     </row>
     <row r="956">
-      <c r="A956" s="2" t="n">
+      <c r="A956" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="B956" t="n">
@@ -45395,7 +45383,7 @@
       </c>
     </row>
     <row r="957">
-      <c r="A957" s="2" t="n">
+      <c r="A957" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="B957" t="n">
@@ -45442,7 +45430,7 @@
       </c>
     </row>
     <row r="958">
-      <c r="A958" s="2" t="n">
+      <c r="A958" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="B958" t="n">
@@ -45489,7 +45477,7 @@
       </c>
     </row>
     <row r="959">
-      <c r="A959" s="2" t="n">
+      <c r="A959" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B959" t="n">
@@ -45536,7 +45524,7 @@
       </c>
     </row>
     <row r="960">
-      <c r="A960" s="2" t="n">
+      <c r="A960" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="B960" t="n">
@@ -45583,7 +45571,7 @@
       </c>
     </row>
     <row r="961">
-      <c r="A961" s="2" t="n">
+      <c r="A961" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="B961" t="n">
@@ -45630,7 +45618,7 @@
       </c>
     </row>
     <row r="962">
-      <c r="A962" s="2" t="n">
+      <c r="A962" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="B962" t="n">

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1143"/>
+  <dimension ref="A1:R1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64464,6 +64464,62 @@
         <v>4637908088</v>
       </c>
     </row>
+    <row r="1144">
+      <c r="A1144" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B1144" t="n">
+        <v>47.1309</v>
+      </c>
+      <c r="C1144" t="n">
+        <v>169144.5793736169</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>77037.46476303233</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>246182.0441366492</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>53285.9913984244</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>14517.8638006064</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>6322.249288683221</v>
+      </c>
+      <c r="I1144" t="n">
+        <v>98437.14811302141</v>
+      </c>
+      <c r="J1144" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1144" t="n">
+        <v>3998.79767</v>
+      </c>
+      <c r="L1144" t="n">
+        <v>-3848.79767</v>
+      </c>
+      <c r="M1144" t="n">
+        <v>49867.31817130586</v>
+      </c>
+      <c r="N1144" t="n">
+        <v>53716.11584130586</v>
+      </c>
+      <c r="O1144" t="n">
+        <v>7971936256</v>
+      </c>
+      <c r="P1144" t="n">
+        <v>684239987</v>
+      </c>
+      <c r="Q1144" t="n">
+        <v>297973299</v>
+      </c>
+      <c r="R1144" t="n">
+        <v>4639431384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1144"/>
+  <dimension ref="A1:R1148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64520,6 +64520,230 @@
         <v>4639431384</v>
       </c>
     </row>
+    <row r="1145">
+      <c r="A1145" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B1145" t="n">
+        <v>47.1467</v>
+      </c>
+      <c r="C1145" t="n">
+        <v>165484.6130057883</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>78215.86380382931</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>243700.4768096176</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>54472.350132671</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>14471.46451395325</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>6297.954893979854</v>
+      </c>
+      <c r="I1145" t="n">
+        <v>97432.20660194669</v>
+      </c>
+      <c r="J1145" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1145" t="n">
+        <v>3739.81692</v>
+      </c>
+      <c r="L1145" t="n">
+        <v>-3589.81692</v>
+      </c>
+      <c r="M1145" t="n">
+        <v>47282.9869959085</v>
+      </c>
+      <c r="N1145" t="n">
+        <v>50872.8039159085</v>
+      </c>
+      <c r="O1145" t="n">
+        <v>7802053404</v>
+      </c>
+      <c r="P1145" t="n">
+        <v>682281796</v>
+      </c>
+      <c r="Q1145" t="n">
+        <v>296927790</v>
+      </c>
+      <c r="R1145" t="n">
+        <v>4593607015</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B1146" t="n">
+        <v>47.1647</v>
+      </c>
+      <c r="C1146" t="n">
+        <v>166348.4980080441</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>77937.77507330693</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>244286.2730813511</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>54203.3229300727</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>14500.3813021179</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>6324.675127796847</v>
+      </c>
+      <c r="I1146" t="n">
+        <v>98376.78346305604</v>
+      </c>
+      <c r="J1146" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1146" t="n">
+        <v>3774.95982</v>
+      </c>
+      <c r="L1146" t="n">
+        <v>-3624.95982</v>
+      </c>
+      <c r="M1146" t="n">
+        <v>47146.65811507335</v>
+      </c>
+      <c r="N1146" t="n">
+        <v>50771.61793507336</v>
+      </c>
+      <c r="O1146" t="n">
+        <v>7845777004</v>
+      </c>
+      <c r="P1146" t="n">
+        <v>683906134</v>
+      </c>
+      <c r="Q1146" t="n">
+        <v>298301405</v>
+      </c>
+      <c r="R1146" t="n">
+        <v>4639911479</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1147" t="n">
+        <v>47.2681</v>
+      </c>
+      <c r="C1147" t="n">
+        <v>168347.4409802806</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>77146.63919218247</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>245494.080172463</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>53464.10668082703</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>14445.38777738052</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>6280.829354257946</v>
+      </c>
+      <c r="I1147" t="n">
+        <v>97323.3226636992</v>
+      </c>
+      <c r="J1147" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1147" t="n">
+        <v>3594.48177</v>
+      </c>
+      <c r="L1147" t="n">
+        <v>-3444.48177</v>
+      </c>
+      <c r="M1147" t="n">
+        <v>50297.90118494291</v>
+      </c>
+      <c r="N1147" t="n">
+        <v>53742.38295494291</v>
+      </c>
+      <c r="O1147" t="n">
+        <v>7957463675</v>
+      </c>
+      <c r="P1147" t="n">
+        <v>682806034</v>
+      </c>
+      <c r="Q1147" t="n">
+        <v>296882870</v>
+      </c>
+      <c r="R1147" t="n">
+        <v>4600288548</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1148" t="n">
+        <v>47.2899</v>
+      </c>
+      <c r="C1148" t="n">
+        <v>169701.8910380441</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>77108.45081084967</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>246810.3418488937</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>53436.83562452024</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>14445.57789295389</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>6280.30991818549</v>
+      </c>
+      <c r="I1148" t="n">
+        <v>96351.11427598704</v>
+      </c>
+      <c r="J1148" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1148" t="n">
+        <v>3752.62035</v>
+      </c>
+      <c r="L1148" t="n">
+        <v>-3602.62035</v>
+      </c>
+      <c r="M1148" t="n">
+        <v>52624.88895091765</v>
+      </c>
+      <c r="N1148" t="n">
+        <v>56227.50930091765</v>
+      </c>
+      <c r="O1148" t="n">
+        <v>8025185457</v>
+      </c>
+      <c r="P1148" t="n">
+        <v>683129934</v>
+      </c>
+      <c r="Q1148" t="n">
+        <v>296995228</v>
+      </c>
+      <c r="R1148" t="n">
+        <v>4556434559</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1148"/>
+  <dimension ref="A1:R1149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64744,6 +64744,62 @@
         <v>4556434559</v>
       </c>
     </row>
+    <row r="1149">
+      <c r="A1149" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1149" t="n">
+        <v>47.3075</v>
+      </c>
+      <c r="C1149" t="n">
+        <v>169149.0983882048</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>75237.47640437563</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>244386.5747925805</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>51574.66786450352</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>14535.81366590921</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>6265.40935369656</v>
+      </c>
+      <c r="I1149" t="n">
+        <v>96402.81405696772</v>
+      </c>
+      <c r="J1149" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1149" t="n">
+        <v>3475.79961</v>
+      </c>
+      <c r="L1149" t="n">
+        <v>-3325.79961</v>
+      </c>
+      <c r="M1149" t="n">
+        <v>51945.06131163136</v>
+      </c>
+      <c r="N1149" t="n">
+        <v>55270.86092163136</v>
+      </c>
+      <c r="O1149" t="n">
+        <v>8002020972</v>
+      </c>
+      <c r="P1149" t="n">
+        <v>687653005</v>
+      </c>
+      <c r="Q1149" t="n">
+        <v>296400853</v>
+      </c>
+      <c r="R1149" t="n">
+        <v>4560576126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1149"/>
+  <dimension ref="A1:R1153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64800,6 +64800,230 @@
         <v>4560576126</v>
       </c>
     </row>
+    <row r="1150">
+      <c r="A1150" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1150" t="n">
+        <v>47.3274</v>
+      </c>
+      <c r="C1150" t="n">
+        <v>167075.8154050297</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>82683.5496350951</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>249759.3650401247</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>58792.14575489041</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>14636.6227808838</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>6294.859869758322</v>
+      </c>
+      <c r="I1150" t="n">
+        <v>96202.44137645424</v>
+      </c>
+      <c r="J1150" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1150" t="n">
+        <v>3395.18924</v>
+      </c>
+      <c r="L1150" t="n">
+        <v>-3245.18924</v>
+      </c>
+      <c r="M1150" t="n">
+        <v>49941.89137793328</v>
+      </c>
+      <c r="N1150" t="n">
+        <v>53187.08061793328</v>
+      </c>
+      <c r="O1150" t="n">
+        <v>7907263946</v>
+      </c>
+      <c r="P1150" t="n">
+        <v>692713301</v>
+      </c>
+      <c r="Q1150" t="n">
+        <v>297919351</v>
+      </c>
+      <c r="R1150" t="n">
+        <v>4553011424</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1151" t="n">
+        <v>47.3452</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>166559.6761656937</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>78662.50139401671</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>245222.1775597104</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>54780.07979689599</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>14545.64164899504</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>6272.92990630518</v>
+      </c>
+      <c r="I1151" t="n">
+        <v>97681.82652095672</v>
+      </c>
+      <c r="J1151" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1151" t="n">
+        <v>3554.61954</v>
+      </c>
+      <c r="L1151" t="n">
+        <v>-3404.61954</v>
+      </c>
+      <c r="M1151" t="n">
+        <v>48059.27808943672</v>
+      </c>
+      <c r="N1151" t="n">
+        <v>51463.89762943672</v>
+      </c>
+      <c r="O1151" t="n">
+        <v>7885801180</v>
+      </c>
+      <c r="P1151" t="n">
+        <v>688666313</v>
+      </c>
+      <c r="Q1151" t="n">
+        <v>296993121</v>
+      </c>
+      <c r="R1151" t="n">
+        <v>4624765613</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B1152" t="n">
+        <v>47.4497</v>
+      </c>
+      <c r="C1152" t="n">
+        <v>170392.928933165</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>78578.54336276099</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>248971.472295926</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>54748.71876956019</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>14542.74319964088</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>6267.430500087461</v>
+      </c>
+      <c r="I1152" t="n">
+        <v>97994.95558454531</v>
+      </c>
+      <c r="J1152" t="n">
+        <v>150</v>
+      </c>
+      <c r="K1152" t="n">
+        <v>3684.96202</v>
+      </c>
+      <c r="L1152" t="n">
+        <v>-3534.96202</v>
+      </c>
+      <c r="M1152" t="n">
+        <v>51587.79964889133</v>
+      </c>
+      <c r="N1152" t="n">
+        <v>55122.76166889133</v>
+      </c>
+      <c r="O1152" t="n">
+        <v>8085093360</v>
+      </c>
+      <c r="P1152" t="n">
+        <v>690048802</v>
+      </c>
+      <c r="Q1152" t="n">
+        <v>297387697</v>
+      </c>
+      <c r="R1152" t="n">
+        <v>4649831244</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1153" t="n">
+        <v>47.4694</v>
+      </c>
+      <c r="C1153" t="n">
+        <v>176131.7272390214</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>79428.48546642679</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>255560.2127054482</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>55608.55037139716</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>14616.11444425251</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>6302.713790357578</v>
+      </c>
+      <c r="I1153" t="n">
+        <v>99539.75441020953</v>
+      </c>
+      <c r="J1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1153" t="n">
+        <v>3778.10231</v>
+      </c>
+      <c r="L1153" t="n">
+        <v>-3778.10231</v>
+      </c>
+      <c r="M1153" t="n">
+        <v>55673.14459420175</v>
+      </c>
+      <c r="N1153" t="n">
+        <v>59451.24690420175</v>
+      </c>
+      <c r="O1153" t="n">
+        <v>8360867413</v>
+      </c>
+      <c r="P1153" t="n">
+        <v>693818183</v>
+      </c>
+      <c r="Q1153" t="n">
+        <v>299186042</v>
+      </c>
+      <c r="R1153" t="n">
+        <v>4725092418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1153"/>
+  <dimension ref="A1:R1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65024,6 +65024,62 @@
         <v>4725092418</v>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1154" t="n">
+        <v>47.4881</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>180770.9446787722</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>79428.99629591413</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>260199.9409746863</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>55618.44108313451</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>14771.10884621621</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>6363.713919908356</v>
+      </c>
+      <c r="I1154" t="n">
+        <v>100321.6651329491</v>
+      </c>
+      <c r="J1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1154" t="n">
+        <v>3684.10496</v>
+      </c>
+      <c r="L1154" t="n">
+        <v>-3684.10496</v>
+      </c>
+      <c r="M1154" t="n">
+        <v>59314.45677969851</v>
+      </c>
+      <c r="N1154" t="n">
+        <v>62998.5617396985</v>
+      </c>
+      <c r="O1154" t="n">
+        <v>8584468698</v>
+      </c>
+      <c r="P1154" t="n">
+        <v>701451894</v>
+      </c>
+      <c r="Q1154" t="n">
+        <v>302200683</v>
+      </c>
+      <c r="R1154" t="n">
+        <v>4764085266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1154"/>
+  <dimension ref="A1:R1158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65080,6 +65080,230 @@
         <v>4764085266</v>
       </c>
     </row>
+    <row r="1155">
+      <c r="A1155" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1155" t="n">
+        <v>47.5055</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>180814.0255970361</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>75983.99160097251</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>256798.0171980087</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>52182.1575607035</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>14792.47034553894</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>6373.502836513668</v>
+      </c>
+      <c r="I1155" t="n">
+        <v>101040.696045721</v>
+      </c>
+      <c r="J1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1155" t="n">
+        <v>3798.92639</v>
+      </c>
+      <c r="L1155" t="n">
+        <v>-3798.92639</v>
+      </c>
+      <c r="M1155" t="n">
+        <v>58607.35636926249</v>
+      </c>
+      <c r="N1155" t="n">
+        <v>62406.28275926249</v>
+      </c>
+      <c r="O1155" t="n">
+        <v>8589660693</v>
+      </c>
+      <c r="P1155" t="n">
+        <v>702723700</v>
+      </c>
+      <c r="Q1155" t="n">
+        <v>302776439</v>
+      </c>
+      <c r="R1155" t="n">
+        <v>4799988786</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1156" t="n">
+        <v>47.5229</v>
+      </c>
+      <c r="C1156" t="n">
+        <v>183554.1558701174</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>78074.95464291953</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>261629.1105130369</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>54281.83536779111</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>14901.28601158599</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>6296.873402086152</v>
+      </c>
+      <c r="I1156" t="n">
+        <v>101982.3704992751</v>
+      </c>
+      <c r="J1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1156" t="n">
+        <v>3744.71427</v>
+      </c>
+      <c r="L1156" t="n">
+        <v>-3744.71427</v>
+      </c>
+      <c r="M1156" t="n">
+        <v>60373.62595717014</v>
+      </c>
+      <c r="N1156" t="n">
+        <v>64118.34022717013</v>
+      </c>
+      <c r="O1156" t="n">
+        <v>8723025794</v>
+      </c>
+      <c r="P1156" t="n">
+        <v>708152325</v>
+      </c>
+      <c r="Q1156" t="n">
+        <v>299245685</v>
+      </c>
+      <c r="R1156" t="n">
+        <v>4846497995</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B1157" t="n">
+        <v>47.626</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>187692.3646957544</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>75384.83133162558</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>263077.19602738</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>51643.21901902322</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>14934.59648091379</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>6322.817263679503</v>
+      </c>
+      <c r="I1157" t="n">
+        <v>102544.3427959518</v>
+      </c>
+      <c r="J1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1157" t="n">
+        <v>3400.18314</v>
+      </c>
+      <c r="L1157" t="n">
+        <v>-3400.18314</v>
+      </c>
+      <c r="M1157" t="n">
+        <v>63890.60815520935</v>
+      </c>
+      <c r="N1157" t="n">
+        <v>67290.79129520935</v>
+      </c>
+      <c r="O1157" t="n">
+        <v>8939036561</v>
+      </c>
+      <c r="P1157" t="n">
+        <v>711275092</v>
+      </c>
+      <c r="Q1157" t="n">
+        <v>301130495</v>
+      </c>
+      <c r="R1157" t="n">
+        <v>4883776870</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1158" t="n">
+        <v>47.6505</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>188021.6789120786</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>77570.39548378297</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>265592.0743958615</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>53840.99018898018</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>14939.56422283082</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>6447.265191341119</v>
+      </c>
+      <c r="I1158" t="n">
+        <v>101757.4327026999</v>
+      </c>
+      <c r="J1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1158" t="n">
+        <v>3275.67593</v>
+      </c>
+      <c r="L1158" t="n">
+        <v>-3275.67593</v>
+      </c>
+      <c r="M1158" t="n">
+        <v>64877.41679520677</v>
+      </c>
+      <c r="N1158" t="n">
+        <v>68153.09272520676</v>
+      </c>
+      <c r="O1158" t="n">
+        <v>8959327011</v>
+      </c>
+      <c r="P1158" t="n">
+        <v>711877705</v>
+      </c>
+      <c r="Q1158" t="n">
+        <v>307215410</v>
+      </c>
+      <c r="R1158" t="n">
+        <v>4848792547</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1159"/>
+  <dimension ref="A1:R1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65360,6 +65360,230 @@
         <v>4843556533</v>
       </c>
     </row>
+    <row r="1160">
+      <c r="A1160" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1160" t="n">
+        <v>47.6858</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>185918.7539477161</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>80150.27897193714</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>266069.0329196532</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>56230.48819564735</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>15420.38237798254</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>6134.142784644486</v>
+      </c>
+      <c r="I1160" t="n">
+        <v>101983.4327200131</v>
+      </c>
+      <c r="J1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1160" t="n">
+        <v>3479.52857</v>
+      </c>
+      <c r="L1160" t="n">
+        <v>-3479.52857</v>
+      </c>
+      <c r="M1160" t="n">
+        <v>62380.79606507596</v>
+      </c>
+      <c r="N1160" t="n">
+        <v>65860.32463507596</v>
+      </c>
+      <c r="O1160" t="n">
+        <v>8865684517</v>
+      </c>
+      <c r="P1160" t="n">
+        <v>735333270</v>
+      </c>
+      <c r="Q1160" t="n">
+        <v>292511506</v>
+      </c>
+      <c r="R1160" t="n">
+        <v>4863161576</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1161" t="n">
+        <v>47.7206</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>187504.8658441009</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>79826.65173950035</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>267331.5175836012</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>55924.30434655055</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>14894.05694815237</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>6171.566199922047</v>
+      </c>
+      <c r="I1161" t="n">
+        <v>103217.1540592532</v>
+      </c>
+      <c r="J1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1161" t="n">
+        <v>3719.94572</v>
+      </c>
+      <c r="L1161" t="n">
+        <v>-3719.94572</v>
+      </c>
+      <c r="M1161" t="n">
+        <v>63222.08863677322</v>
+      </c>
+      <c r="N1161" t="n">
+        <v>66942.03435677322</v>
+      </c>
+      <c r="O1161" t="n">
+        <v>8947844701</v>
+      </c>
+      <c r="P1161" t="n">
+        <v>710753334</v>
+      </c>
+      <c r="Q1161" t="n">
+        <v>294510842</v>
+      </c>
+      <c r="R1161" t="n">
+        <v>4925584522</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1162" t="n">
+        <v>47.8109</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>189790.7186645723</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>78839.15420960494</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>268629.8728741773</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>54981.95095679019</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>14891.45362250031</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>6153.60967896442</v>
+      </c>
+      <c r="I1162" t="n">
+        <v>103597.5078067972</v>
+      </c>
+      <c r="J1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1162" t="n">
+        <v>4012.24062</v>
+      </c>
+      <c r="L1162" t="n">
+        <v>-4012.24062</v>
+      </c>
+      <c r="M1162" t="n">
+        <v>65148.14755631042</v>
+      </c>
+      <c r="N1162" t="n">
+        <v>69160.38817631041</v>
+      </c>
+      <c r="O1162" t="n">
+        <v>9074065071</v>
+      </c>
+      <c r="P1162" t="n">
+        <v>711973800</v>
+      </c>
+      <c r="Q1162" t="n">
+        <v>294209617</v>
+      </c>
+      <c r="R1162" t="n">
+        <v>4953090086</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1163" t="n">
+        <v>47.8293</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>188421.1384444263</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>78261.64016617427</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>266682.7786106006</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>54413.61481351389</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>14952.12514086554</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>6017.052078955786</v>
+      </c>
+      <c r="I1163" t="n">
+        <v>104062.2370597103</v>
+      </c>
+      <c r="J1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1163" t="n">
+        <v>4215.53175</v>
+      </c>
+      <c r="L1163" t="n">
+        <v>-4215.53175</v>
+      </c>
+      <c r="M1163" t="n">
+        <v>63389.72416489472</v>
+      </c>
+      <c r="N1163" t="n">
+        <v>67605.25591489472</v>
+      </c>
+      <c r="O1163" t="n">
+        <v>9012051157</v>
+      </c>
+      <c r="P1163" t="n">
+        <v>715149679</v>
+      </c>
+      <c r="Q1163" t="n">
+        <v>287791389</v>
+      </c>
+      <c r="R1163" t="n">
+        <v>4977223955</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1169"/>
+  <dimension ref="A1:R1173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65920,6 +65920,230 @@
         <v>5154652033</v>
       </c>
     </row>
+    <row r="1170">
+      <c r="A1170" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1170" t="n">
+        <v>48.0466</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>191258.348769736</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>83150.52424104932</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>274408.8730107854</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>58897.54382203944</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>15145.99667822489</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>6078.017549628902</v>
+      </c>
+      <c r="I1170" t="n">
+        <v>106939.2803236858</v>
+      </c>
+      <c r="J1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1170" t="n">
+        <v>5784.81961</v>
+      </c>
+      <c r="L1170" t="n">
+        <v>-5784.81961</v>
+      </c>
+      <c r="M1170" t="n">
+        <v>63095.05421819648</v>
+      </c>
+      <c r="N1170" t="n">
+        <v>68879.87382819649</v>
+      </c>
+      <c r="O1170" t="n">
+        <v>9189313380</v>
+      </c>
+      <c r="P1170" t="n">
+        <v>727713644</v>
+      </c>
+      <c r="Q1170" t="n">
+        <v>292028078</v>
+      </c>
+      <c r="R1170" t="n">
+        <v>5138068826</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>48.0732</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>189441.3038657714</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>82546.23139295907</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>271987.5352587304</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>58306.67070217918</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>15142.85913981179</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>6130.494329480875</v>
+      </c>
+      <c r="I1171" t="n">
+        <v>106043.2105414243</v>
+      </c>
+      <c r="J1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1171" t="n">
+        <v>5642.83519</v>
+      </c>
+      <c r="L1171" t="n">
+        <v>-5642.83519</v>
+      </c>
+      <c r="M1171" t="n">
+        <v>62124.73985505437</v>
+      </c>
+      <c r="N1171" t="n">
+        <v>67767.57504505437</v>
+      </c>
+      <c r="O1171" t="n">
+        <v>9107049689</v>
+      </c>
+      <c r="P1171" t="n">
+        <v>727965696</v>
+      </c>
+      <c r="Q1171" t="n">
+        <v>294712480</v>
+      </c>
+      <c r="R1171" t="n">
+        <v>5097836469</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>48.1745</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>184420.633862313</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>80348.98952765466</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>264769.6233899677</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>56160.39911156317</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>14853.52663753646</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>5925.385836905416</v>
+      </c>
+      <c r="I1172" t="n">
+        <v>103954.7752856802</v>
+      </c>
+      <c r="J1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1172" t="n">
+        <v>5431.33004</v>
+      </c>
+      <c r="L1172" t="n">
+        <v>-5431.33004</v>
+      </c>
+      <c r="M1172" t="n">
+        <v>59686.94610219098</v>
+      </c>
+      <c r="N1172" t="n">
+        <v>65118.27614219098</v>
+      </c>
+      <c r="O1172" t="n">
+        <v>8884371826</v>
+      </c>
+      <c r="P1172" t="n">
+        <v>715561219</v>
+      </c>
+      <c r="Q1172" t="n">
+        <v>285452500</v>
+      </c>
+      <c r="R1172" t="n">
+        <v>5007969322</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>48.1891</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>183506.8472953427</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>81171.54271401624</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>264678.3900093589</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>56990.28078963915</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>14796.48285608156</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>5873.148969372742</v>
+      </c>
+      <c r="I1173" t="n">
+        <v>103431.9127562042</v>
+      </c>
+      <c r="J1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1173" t="n">
+        <v>5416.55092</v>
+      </c>
+      <c r="L1173" t="n">
+        <v>-5416.55092</v>
+      </c>
+      <c r="M1173" t="n">
+        <v>59405.30271368421</v>
+      </c>
+      <c r="N1173" t="n">
+        <v>64821.85363368422</v>
+      </c>
+      <c r="O1173" t="n">
+        <v>8843029815</v>
+      </c>
+      <c r="P1173" t="n">
+        <v>713029192</v>
+      </c>
+      <c r="Q1173" t="n">
+        <v>283021763</v>
+      </c>
+      <c r="R1173" t="n">
+        <v>4984290787</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1173"/>
+  <dimension ref="A1:R1174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66144,6 +66144,62 @@
         <v>4984290787</v>
       </c>
     </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>48.2075</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>186244.3259866203</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>81205.06645231551</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>267449.3924389358</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>57033.03411294923</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>14945.64132137115</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>5941.429881242545</v>
+      </c>
+      <c r="I1174" t="n">
+        <v>104450.4662759944</v>
+      </c>
+      <c r="J1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1174" t="n">
+        <v>5064.37621</v>
+      </c>
+      <c r="L1174" t="n">
+        <v>-5064.37621</v>
+      </c>
+      <c r="M1174" t="n">
+        <v>60906.78850801224</v>
+      </c>
+      <c r="N1174" t="n">
+        <v>65971.16471801224</v>
+      </c>
+      <c r="O1174" t="n">
+        <v>8978373345</v>
+      </c>
+      <c r="P1174" t="n">
+        <v>720492004</v>
+      </c>
+      <c r="Q1174" t="n">
+        <v>286421481</v>
+      </c>
+      <c r="R1174" t="n">
+        <v>5035295853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
